--- a/data/data_minerals/USGS/Mineral_yearbook/myb1-2023-plati-ERT.xlsx
+++ b/data/data_minerals/USGS/Mineral_yearbook/myb1-2023-plati-ERT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WebPosts\todo20250206\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/plca_metals_github/plca_metals/data/data_minerals/USGS/Mineral_yearbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F071FA52-E7B9-4BB0-A7AA-FD209C57079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{F071FA52-E7B9-4BB0-A7AA-FD209C57079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4606CF6-2232-4D83-ACC8-696593C5E7B9}"/>
   <bookViews>
-    <workbookView xWindow="3345" yWindow="1065" windowWidth="15810" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="31" r:id="rId1"/>
@@ -1372,12 +1372,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="#,###"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,###"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="45" x14ac:knownFonts="1">
     <font>
@@ -1684,7 +1684,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1873,6 +1873,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2217,10 +2223,10 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2289,7 +2295,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2332,13 +2338,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="94" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="95" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="95" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="37" fillId="0" borderId="0" xfId="94" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -2457,8 +2463,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="91" applyNumberFormat="1" applyFont="1"/>
@@ -2501,11 +2507,11 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -2517,7 +2523,7 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2532,7 +2538,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -2592,27 +2598,8 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="91" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
@@ -2644,7 +2631,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="160" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="2" xfId="160" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2658,13 +2645,13 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2694,13 +2681,13 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2746,21 +2733,71 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="95" applyFont="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="91" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="95" applyFont="1"/>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="91" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="3" xfId="91" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="91" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="91" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="161"/>
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="18" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" xfId="161" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="19" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="161" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="20" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="21" xfId="161" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="22" xfId="161" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="18" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" xfId="161" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="19" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="18" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" xfId="161" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="19" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="34" borderId="15" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="34" borderId="16" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="34" borderId="17" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="18" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="0" xfId="162" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="19" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2881,61 +2918,11 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="3" xfId="91" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="161"/>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="15" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="16" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="17" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="18" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="0" xfId="162" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="19" xfId="162" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="18" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" xfId="161" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="19" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="161" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="18" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" xfId="161" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="19" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="18" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" xfId="161" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="19" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="20" xfId="161" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="21" xfId="161" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="22" xfId="161" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
+    <xf numFmtId="3" fontId="17" fillId="35" borderId="3" xfId="92" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="35" borderId="13" xfId="92" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="163">
@@ -3465,168 +3452,168 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A4:L14"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="189" customWidth="1"/>
-    <col min="2" max="16384" width="10.6640625" style="189"/>
+    <col min="1" max="1" width="10.5" style="147" customWidth="1"/>
+    <col min="2" max="16384" width="10.6640625" style="147"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="190" t="s">
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="161" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="191"/>
-      <c r="C5" s="191"/>
-      <c r="D5" s="191"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="191"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
-      <c r="L5" s="192"/>
-    </row>
-    <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="193" t="s">
+      <c r="B5" s="162"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="162"/>
+      <c r="I5" s="162"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="163"/>
+    </row>
+    <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="164" t="s">
         <v>187</v>
       </c>
-      <c r="B6" s="194"/>
-      <c r="C6" s="194"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="194"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="195"/>
-    </row>
-    <row r="7" spans="1:12" s="199" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A7" s="196" t="s">
+      <c r="B6" s="165"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="165"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="166"/>
+    </row>
+    <row r="7" spans="1:12" s="151" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="155" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="197"/>
-      <c r="C7" s="197"/>
-      <c r="D7" s="197"/>
-      <c r="E7" s="197"/>
-      <c r="F7" s="197"/>
-      <c r="G7" s="197"/>
-      <c r="H7" s="197"/>
-      <c r="I7" s="197"/>
-      <c r="J7" s="197"/>
-      <c r="K7" s="197"/>
-      <c r="L7" s="198"/>
-    </row>
-    <row r="8" spans="1:12" s="199" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A8" s="196" t="s">
+      <c r="B7" s="156"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
+      <c r="K7" s="156"/>
+      <c r="L7" s="157"/>
+    </row>
+    <row r="8" spans="1:12" s="151" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="155" t="s">
         <v>189</v>
       </c>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="197"/>
-      <c r="E8" s="197"/>
-      <c r="F8" s="197"/>
-      <c r="G8" s="197"/>
-      <c r="H8" s="197"/>
-      <c r="I8" s="197"/>
-      <c r="J8" s="197"/>
-      <c r="K8" s="197"/>
-      <c r="L8" s="198"/>
-    </row>
-    <row r="9" spans="1:12" s="199" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A9" s="196" t="s">
+      <c r="B8" s="156"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="156"/>
+      <c r="J8" s="156"/>
+      <c r="K8" s="156"/>
+      <c r="L8" s="157"/>
+    </row>
+    <row r="9" spans="1:12" s="151" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="197"/>
-      <c r="E9" s="197"/>
-      <c r="F9" s="197"/>
-      <c r="G9" s="197"/>
-      <c r="H9" s="197"/>
-      <c r="I9" s="197"/>
-      <c r="J9" s="197"/>
-      <c r="K9" s="197"/>
-      <c r="L9" s="198"/>
-    </row>
-    <row r="10" spans="1:12" s="199" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A10" s="196" t="s">
+      <c r="B9" s="156"/>
+      <c r="C9" s="156"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="156"/>
+      <c r="I9" s="156"/>
+      <c r="J9" s="156"/>
+      <c r="K9" s="156"/>
+      <c r="L9" s="157"/>
+    </row>
+    <row r="10" spans="1:12" s="151" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="B10" s="197"/>
-      <c r="C10" s="197"/>
-      <c r="D10" s="197"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="197"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="197"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="197"/>
-      <c r="L10" s="198"/>
-    </row>
-    <row r="11" spans="1:12" s="199" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A11" s="196" t="s">
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="156"/>
+      <c r="I10" s="156"/>
+      <c r="J10" s="156"/>
+      <c r="K10" s="156"/>
+      <c r="L10" s="157"/>
+    </row>
+    <row r="11" spans="1:12" s="151" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="197"/>
-      <c r="L11" s="198"/>
-    </row>
-    <row r="12" spans="1:12" s="199" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A12" s="200"/>
-      <c r="B12" s="201"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="201"/>
-      <c r="F12" s="201"/>
-      <c r="G12" s="201"/>
-      <c r="H12" s="201"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="202"/>
-    </row>
-    <row r="13" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="203" t="s">
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
+      <c r="J11" s="156"/>
+      <c r="K11" s="156"/>
+      <c r="L11" s="157"/>
+    </row>
+    <row r="12" spans="1:12" s="151" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="148"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="149"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="149"/>
+      <c r="L12" s="150"/>
+    </row>
+    <row r="13" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="158" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="204"/>
-      <c r="H13" s="204"/>
-      <c r="I13" s="204"/>
-      <c r="J13" s="204"/>
-      <c r="K13" s="204"/>
-      <c r="L13" s="205"/>
-    </row>
-    <row r="14" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="206"/>
-      <c r="B14" s="207"/>
-      <c r="C14" s="207"/>
-      <c r="D14" s="207"/>
-      <c r="E14" s="207"/>
-      <c r="F14" s="207"/>
-      <c r="G14" s="207"/>
-      <c r="H14" s="207"/>
-      <c r="I14" s="207"/>
-      <c r="J14" s="207"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="208"/>
+      <c r="B13" s="159"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
+      <c r="L13" s="160"/>
+    </row>
+    <row r="14" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="152"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="153"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="153"/>
+      <c r="H14" s="153"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="153"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3648,7 +3635,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9375CE86-49DC-4645-96DF-9F03B0AACDBB}">
   <dimension ref="A1:U58"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.83203125" style="26" customWidth="1"/>
     <col min="2" max="2" width="21" style="26" customWidth="1"/>
@@ -3667,50 +3654,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
     </row>
     <row r="2" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="171" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
     </row>
     <row r="3" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="159"/>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
+      <c r="A3" s="172"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="172"/>
     </row>
     <row r="4" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -3785,325 +3772,325 @@
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="108" t="s">
+      <c r="A8" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="109" t="s">
+      <c r="B8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111">
+      <c r="C8" s="105"/>
+      <c r="D8" s="106">
         <v>14300</v>
       </c>
-      <c r="E8" s="112"/>
-      <c r="F8" s="111">
+      <c r="E8" s="107"/>
+      <c r="F8" s="106">
         <v>14600</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="111">
+      <c r="G8" s="107"/>
+      <c r="H8" s="106">
         <v>13700</v>
       </c>
-      <c r="I8" s="112"/>
-      <c r="J8" s="111">
+      <c r="I8" s="107"/>
+      <c r="J8" s="106">
         <v>10100</v>
       </c>
-      <c r="K8" s="112"/>
-      <c r="L8" s="111">
+      <c r="K8" s="107"/>
+      <c r="L8" s="106">
         <v>10300</v>
       </c>
       <c r="M8" s="15"/>
     </row>
     <row r="9" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="116">
+      <c r="C9" s="110"/>
+      <c r="D9" s="111">
         <v>711000</v>
       </c>
-      <c r="E9" s="117"/>
-      <c r="F9" s="116">
+      <c r="E9" s="112"/>
+      <c r="F9" s="111">
         <v>1030000</v>
       </c>
-      <c r="G9" s="117"/>
-      <c r="H9" s="116">
+      <c r="G9" s="112"/>
+      <c r="H9" s="111">
         <v>1070000</v>
       </c>
-      <c r="I9" s="117"/>
-      <c r="J9" s="116">
+      <c r="I9" s="112"/>
+      <c r="J9" s="111">
         <v>693000</v>
       </c>
-      <c r="K9" s="117"/>
-      <c r="L9" s="116">
+      <c r="K9" s="112"/>
+      <c r="L9" s="111">
         <v>445000</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="114"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="120"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="115"/>
     </row>
     <row r="11" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="108" t="s">
+      <c r="A11" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="109" t="s">
+      <c r="B11" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="110"/>
-      <c r="D11" s="111">
+      <c r="C11" s="105"/>
+      <c r="D11" s="106">
         <v>4150</v>
       </c>
-      <c r="E11" s="112"/>
-      <c r="F11" s="111">
+      <c r="E11" s="107"/>
+      <c r="F11" s="106">
         <v>4200</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="111">
+      <c r="G11" s="107"/>
+      <c r="H11" s="106">
         <v>4020</v>
       </c>
-      <c r="I11" s="112"/>
-      <c r="J11" s="111">
+      <c r="I11" s="107"/>
+      <c r="J11" s="106">
         <v>3000</v>
       </c>
-      <c r="K11" s="112"/>
-      <c r="L11" s="111">
+      <c r="K11" s="107"/>
+      <c r="L11" s="106">
         <v>3040</v>
       </c>
       <c r="M11" s="15"/>
     </row>
     <row r="12" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="116">
+      <c r="C12" s="110"/>
+      <c r="D12" s="111">
         <v>116000</v>
       </c>
-      <c r="E12" s="122"/>
-      <c r="F12" s="116">
+      <c r="E12" s="117"/>
+      <c r="F12" s="111">
         <v>120000</v>
       </c>
-      <c r="G12" s="122"/>
-      <c r="H12" s="116">
+      <c r="G12" s="117"/>
+      <c r="H12" s="111">
         <v>141000</v>
       </c>
-      <c r="I12" s="122"/>
-      <c r="J12" s="116">
+      <c r="I12" s="117"/>
+      <c r="J12" s="111">
         <v>93300</v>
       </c>
-      <c r="K12" s="122"/>
-      <c r="L12" s="116">
+      <c r="K12" s="117"/>
+      <c r="L12" s="111">
         <v>95000</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="118" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="114"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="120"/>
-      <c r="K13" s="125"/>
-      <c r="L13" s="120"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="115"/>
     </row>
     <row r="14" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="127"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="122"/>
     </row>
     <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="108" t="s">
+      <c r="A15" s="103" t="s">
         <v>158</v>
       </c>
-      <c r="B15" s="109" t="s">
+      <c r="B15" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="128">
+      <c r="C15" s="105"/>
+      <c r="D15" s="123">
         <v>65800</v>
       </c>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="F15" s="129">
+      <c r="F15" s="124">
         <v>53300</v>
       </c>
-      <c r="G15" s="130" t="s">
+      <c r="G15" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="H15" s="129">
+      <c r="H15" s="124">
         <v>78700</v>
       </c>
-      <c r="I15" s="130" t="s">
+      <c r="I15" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="J15" s="129">
+      <c r="J15" s="124">
         <v>56100</v>
       </c>
-      <c r="K15" s="130" t="s">
+      <c r="K15" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="L15" s="129">
+      <c r="L15" s="124">
         <v>56200</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="113" t="s">
+      <c r="A16" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="115"/>
-      <c r="D16" s="131">
+      <c r="C16" s="110"/>
+      <c r="D16" s="126">
         <v>3260000</v>
       </c>
-      <c r="E16" s="117" t="s">
+      <c r="E16" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="F16" s="132">
+      <c r="F16" s="127">
         <v>3780000</v>
       </c>
-      <c r="G16" s="130" t="s">
+      <c r="G16" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="H16" s="132">
+      <c r="H16" s="127">
         <v>6120000</v>
       </c>
-      <c r="I16" s="130" t="s">
+      <c r="I16" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="J16" s="132">
+      <c r="J16" s="127">
         <v>3850000</v>
       </c>
-      <c r="K16" s="130" t="s">
+      <c r="K16" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="L16" s="132">
+      <c r="L16" s="127">
         <v>2440000</v>
       </c>
       <c r="M16" s="19"/>
     </row>
     <row r="17" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="133"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="133"/>
+      <c r="B17" s="109"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="128"/>
     </row>
     <row r="18" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="103" t="s">
         <v>158</v>
       </c>
-      <c r="B18" s="109" t="s">
+      <c r="B18" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="128">
+      <c r="C18" s="105"/>
+      <c r="D18" s="123">
         <v>37900</v>
       </c>
-      <c r="E18" s="117" t="s">
+      <c r="E18" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="F18" s="129">
+      <c r="F18" s="124">
         <v>38300</v>
       </c>
-      <c r="G18" s="130" t="s">
+      <c r="G18" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="H18" s="129">
+      <c r="H18" s="124">
         <v>40800</v>
       </c>
-      <c r="I18" s="130" t="s">
+      <c r="I18" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="J18" s="129">
+      <c r="J18" s="124">
         <v>32100</v>
       </c>
-      <c r="K18" s="130" t="s">
+      <c r="K18" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="L18" s="129">
+      <c r="L18" s="124">
         <v>32900</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="115"/>
-      <c r="D19" s="131">
+      <c r="C19" s="110"/>
+      <c r="D19" s="126">
         <v>1060000</v>
       </c>
-      <c r="E19" s="117" t="s">
+      <c r="E19" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="F19" s="132">
+      <c r="F19" s="127">
         <v>1090000</v>
       </c>
-      <c r="G19" s="130" t="s">
+      <c r="G19" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="H19" s="132">
+      <c r="H19" s="127">
         <v>1440000</v>
       </c>
-      <c r="I19" s="130" t="s">
+      <c r="I19" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="J19" s="132">
+      <c r="J19" s="127">
         <v>998000</v>
       </c>
-      <c r="K19" s="130" t="s">
+      <c r="K19" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="L19" s="132">
+      <c r="L19" s="127">
         <v>1030000</v>
       </c>
       <c r="M19" s="18"/>
@@ -4112,196 +4099,196 @@
       <c r="T19" s="17"/>
     </row>
     <row r="20" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="114"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="120"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="115"/>
       <c r="T20" s="17"/>
     </row>
     <row r="21" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="118" t="s">
+      <c r="A21" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="109" t="s">
+      <c r="B21" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="129">
+      <c r="C21" s="105"/>
+      <c r="D21" s="124">
         <v>875</v>
       </c>
-      <c r="E21" s="135"/>
-      <c r="F21" s="129">
+      <c r="E21" s="130"/>
+      <c r="F21" s="124">
         <v>1620</v>
       </c>
-      <c r="G21" s="135"/>
-      <c r="H21" s="129">
+      <c r="G21" s="130"/>
+      <c r="H21" s="124">
         <v>2310</v>
       </c>
-      <c r="I21" s="135"/>
-      <c r="J21" s="129">
+      <c r="I21" s="130"/>
+      <c r="J21" s="124">
         <v>1610</v>
       </c>
-      <c r="K21" s="135"/>
-      <c r="L21" s="129">
+      <c r="K21" s="130"/>
+      <c r="L21" s="124">
         <v>2040</v>
       </c>
       <c r="T21" s="17"/>
     </row>
     <row r="22" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="118" t="s">
+      <c r="A22" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="114" t="s">
+      <c r="B22" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="115"/>
+      <c r="C22" s="110"/>
       <c r="D22" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="135"/>
+      <c r="E22" s="130"/>
       <c r="F22" s="31">
         <v>1</v>
       </c>
-      <c r="G22" s="135"/>
+      <c r="G22" s="130"/>
       <c r="H22" s="31">
         <v>1</v>
       </c>
-      <c r="I22" s="135"/>
+      <c r="I22" s="130"/>
       <c r="J22" s="31">
         <v>1</v>
       </c>
-      <c r="K22" s="135"/>
+      <c r="K22" s="130"/>
       <c r="L22" s="59" t="s">
         <v>103</v>
       </c>
       <c r="T22" s="17"/>
     </row>
     <row r="23" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="118" t="s">
+      <c r="A23" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="114" t="s">
+      <c r="B23" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="115"/>
-      <c r="D23" s="136">
+      <c r="C23" s="110"/>
+      <c r="D23" s="131">
         <v>84300</v>
       </c>
-      <c r="E23" s="135"/>
-      <c r="F23" s="136">
+      <c r="E23" s="130"/>
+      <c r="F23" s="131">
         <v>76400</v>
       </c>
-      <c r="G23" s="135"/>
-      <c r="H23" s="136">
+      <c r="G23" s="130"/>
+      <c r="H23" s="131">
         <v>72600</v>
       </c>
-      <c r="I23" s="135"/>
-      <c r="J23" s="136">
+      <c r="I23" s="130"/>
+      <c r="J23" s="131">
         <v>65200</v>
       </c>
-      <c r="K23" s="135"/>
-      <c r="L23" s="136">
+      <c r="K23" s="130"/>
+      <c r="L23" s="131">
         <v>66900</v>
       </c>
       <c r="T23" s="17"/>
     </row>
     <row r="24" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="118" t="s">
+      <c r="A24" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="114" t="s">
+      <c r="B24" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="115"/>
-      <c r="D24" s="137">
+      <c r="C24" s="110"/>
+      <c r="D24" s="132">
         <v>42300</v>
       </c>
-      <c r="E24" s="138"/>
-      <c r="F24" s="137">
+      <c r="E24" s="133"/>
+      <c r="F24" s="132">
         <v>64900</v>
       </c>
-      <c r="G24" s="138" t="s">
+      <c r="G24" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="137">
+      <c r="H24" s="132">
         <v>67900</v>
       </c>
-      <c r="I24" s="138"/>
-      <c r="J24" s="137">
+      <c r="I24" s="133"/>
+      <c r="J24" s="132">
         <v>64200</v>
       </c>
-      <c r="K24" s="138"/>
-      <c r="L24" s="137">
+      <c r="K24" s="133"/>
+      <c r="L24" s="132">
         <v>66800</v>
       </c>
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
     </row>
     <row r="25" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="129">
+      <c r="C25" s="110"/>
+      <c r="D25" s="124">
         <v>15000</v>
       </c>
-      <c r="E25" s="139"/>
-      <c r="F25" s="129">
+      <c r="E25" s="134"/>
+      <c r="F25" s="124">
         <v>20700</v>
       </c>
-      <c r="G25" s="139"/>
-      <c r="H25" s="129">
+      <c r="G25" s="134"/>
+      <c r="H25" s="124">
         <v>16500</v>
       </c>
-      <c r="I25" s="139"/>
-      <c r="J25" s="129">
+      <c r="I25" s="134"/>
+      <c r="J25" s="124">
         <v>13200</v>
       </c>
-      <c r="K25" s="139"/>
-      <c r="L25" s="129">
+      <c r="K25" s="134"/>
+      <c r="L25" s="124">
         <v>12100</v>
       </c>
       <c r="T25" s="17"/>
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="118" t="s">
+      <c r="A26" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="114" t="s">
+      <c r="B26" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="115"/>
-      <c r="D26" s="129">
+      <c r="C26" s="110"/>
+      <c r="D26" s="124">
         <v>11200</v>
       </c>
-      <c r="E26" s="135"/>
-      <c r="F26" s="129">
+      <c r="E26" s="130"/>
+      <c r="F26" s="124">
         <v>13900</v>
       </c>
-      <c r="G26" s="135"/>
-      <c r="H26" s="129">
+      <c r="G26" s="130"/>
+      <c r="H26" s="124">
         <v>18000</v>
       </c>
-      <c r="I26" s="135"/>
-      <c r="J26" s="129">
+      <c r="I26" s="130"/>
+      <c r="J26" s="124">
         <v>13300</v>
       </c>
-      <c r="K26" s="135"/>
-      <c r="L26" s="129">
+      <c r="K26" s="130"/>
+      <c r="L26" s="124">
         <v>10800</v>
       </c>
       <c r="S26" s="17"/>
@@ -4309,419 +4296,419 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="118" t="s">
+      <c r="A27" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="114" t="s">
+      <c r="B27" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="136">
+      <c r="C27" s="110"/>
+      <c r="D27" s="131">
         <v>35200</v>
       </c>
-      <c r="E27" s="140"/>
-      <c r="F27" s="136">
+      <c r="E27" s="135"/>
+      <c r="F27" s="131">
         <v>185000</v>
       </c>
-      <c r="G27" s="140"/>
-      <c r="H27" s="136">
+      <c r="G27" s="135"/>
+      <c r="H27" s="131">
         <v>160000</v>
       </c>
-      <c r="I27" s="140" t="s">
+      <c r="I27" s="135" t="s">
         <v>160</v>
       </c>
-      <c r="J27" s="136">
+      <c r="J27" s="131">
         <v>41500</v>
       </c>
-      <c r="K27" s="140" t="s">
+      <c r="K27" s="135" t="s">
         <v>160</v>
       </c>
-      <c r="L27" s="136">
+      <c r="L27" s="131">
         <v>32000</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="123" t="s">
+      <c r="A28" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="114"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="141"/>
-      <c r="I28" s="142"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="141"/>
+      <c r="B28" s="109"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="137"/>
+      <c r="L28" s="136"/>
       <c r="T28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="118" t="s">
+      <c r="A29" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="109" t="s">
+      <c r="B29" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="129">
+      <c r="C29" s="105"/>
+      <c r="D29" s="124">
         <v>1330</v>
       </c>
-      <c r="E29" s="130"/>
-      <c r="F29" s="129">
+      <c r="E29" s="125"/>
+      <c r="F29" s="124">
         <v>1440</v>
       </c>
-      <c r="G29" s="130"/>
-      <c r="H29" s="129">
+      <c r="G29" s="125"/>
+      <c r="H29" s="124">
         <v>2180</v>
       </c>
-      <c r="I29" s="130"/>
-      <c r="J29" s="129">
+      <c r="I29" s="125"/>
+      <c r="J29" s="124">
         <v>1010</v>
       </c>
-      <c r="K29" s="130" t="s">
+      <c r="K29" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="L29" s="129">
+      <c r="L29" s="124">
         <v>845</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="118" t="s">
+      <c r="A30" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="114" t="s">
+      <c r="B30" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="115"/>
-      <c r="D30" s="129">
+      <c r="C30" s="110"/>
+      <c r="D30" s="124">
         <v>55500</v>
       </c>
-      <c r="E30" s="130"/>
-      <c r="F30" s="129">
+      <c r="E30" s="125"/>
+      <c r="F30" s="124">
         <v>48600</v>
       </c>
-      <c r="G30" s="130"/>
-      <c r="H30" s="129">
+      <c r="G30" s="125"/>
+      <c r="H30" s="124">
         <v>43900</v>
       </c>
-      <c r="I30" s="130"/>
-      <c r="J30" s="129">
+      <c r="I30" s="125"/>
+      <c r="J30" s="124">
         <v>42200</v>
       </c>
-      <c r="K30" s="130"/>
-      <c r="L30" s="129">
+      <c r="K30" s="125"/>
+      <c r="L30" s="124">
         <v>33600</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="118" t="s">
+      <c r="A31" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="114" t="s">
+      <c r="B31" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="115"/>
-      <c r="D31" s="129">
+      <c r="C31" s="110"/>
+      <c r="D31" s="124">
         <v>17400</v>
       </c>
-      <c r="E31" s="135"/>
-      <c r="F31" s="129">
+      <c r="E31" s="130"/>
+      <c r="F31" s="124">
         <v>28900</v>
       </c>
-      <c r="G31" s="135"/>
-      <c r="H31" s="129">
+      <c r="G31" s="130"/>
+      <c r="H31" s="124">
         <v>29400</v>
       </c>
-      <c r="I31" s="135"/>
-      <c r="J31" s="129">
+      <c r="I31" s="130"/>
+      <c r="J31" s="124">
         <v>23100</v>
       </c>
-      <c r="K31" s="135" t="s">
+      <c r="K31" s="130" t="s">
         <v>160</v>
       </c>
-      <c r="L31" s="129">
+      <c r="L31" s="124">
         <v>11300</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="118" t="s">
+      <c r="A32" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="114" t="s">
+      <c r="B32" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="115"/>
-      <c r="D32" s="129">
+      <c r="C32" s="110"/>
+      <c r="D32" s="124">
         <v>1210</v>
       </c>
-      <c r="E32" s="130"/>
-      <c r="F32" s="129">
+      <c r="E32" s="125"/>
+      <c r="F32" s="124">
         <v>1480</v>
       </c>
-      <c r="G32" s="130"/>
-      <c r="H32" s="129">
+      <c r="G32" s="125"/>
+      <c r="H32" s="124">
         <v>1350</v>
       </c>
-      <c r="I32" s="130"/>
-      <c r="J32" s="129">
+      <c r="I32" s="125"/>
+      <c r="J32" s="124">
         <v>717</v>
       </c>
-      <c r="K32" s="135" t="s">
+      <c r="K32" s="130" t="s">
         <v>160</v>
       </c>
-      <c r="L32" s="129">
+      <c r="L32" s="124">
         <v>453</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="118" t="s">
+      <c r="A33" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="114" t="s">
+      <c r="B33" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="115"/>
-      <c r="D33" s="136">
+      <c r="C33" s="110"/>
+      <c r="D33" s="131">
         <v>20800</v>
       </c>
-      <c r="E33" s="140"/>
-      <c r="F33" s="136">
+      <c r="E33" s="135"/>
+      <c r="F33" s="131">
         <v>33200</v>
       </c>
-      <c r="G33" s="140"/>
-      <c r="H33" s="136">
+      <c r="G33" s="135"/>
+      <c r="H33" s="131">
         <v>37800</v>
       </c>
-      <c r="I33" s="140"/>
-      <c r="J33" s="136">
+      <c r="I33" s="135"/>
+      <c r="J33" s="131">
         <v>35200</v>
       </c>
-      <c r="K33" s="140" t="s">
+      <c r="K33" s="135" t="s">
         <v>160</v>
       </c>
-      <c r="L33" s="136">
+      <c r="L33" s="131">
         <v>13900</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="123" t="s">
+      <c r="A34" s="118" t="s">
         <v>112</v>
       </c>
-      <c r="B34" s="114"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="127"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="127"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="119"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="122"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="122"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="122"/>
     </row>
     <row r="35" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="126" t="s">
+      <c r="A35" s="121" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="109" t="s">
+      <c r="B35" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="143">
+      <c r="C35" s="105"/>
+      <c r="D35" s="138">
         <v>1485.8</v>
       </c>
-      <c r="E35" s="144"/>
-      <c r="F35" s="143">
+      <c r="E35" s="139"/>
+      <c r="F35" s="138">
         <v>1633.51</v>
       </c>
-      <c r="G35" s="144"/>
-      <c r="H35" s="143">
+      <c r="G35" s="139"/>
+      <c r="H35" s="138">
         <v>5158.3999999999996</v>
       </c>
-      <c r="I35" s="144"/>
-      <c r="J35" s="143">
+      <c r="I35" s="139"/>
+      <c r="J35" s="138">
         <v>4581.93</v>
       </c>
-      <c r="K35" s="144"/>
-      <c r="L35" s="143">
+      <c r="K35" s="139"/>
+      <c r="L35" s="138">
         <v>4672.78</v>
       </c>
       <c r="M35" s="12"/>
       <c r="P35" s="16"/>
     </row>
     <row r="36" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="115"/>
-      <c r="D36" s="143">
+      <c r="C36" s="110"/>
+      <c r="D36" s="138">
         <v>1544.31</v>
       </c>
-      <c r="E36" s="144"/>
-      <c r="F36" s="143">
+      <c r="E36" s="139"/>
+      <c r="F36" s="138">
         <v>2205.27</v>
       </c>
-      <c r="G36" s="144"/>
-      <c r="H36" s="143">
+      <c r="G36" s="139"/>
+      <c r="H36" s="138">
         <v>2419.1799999999998</v>
       </c>
-      <c r="I36" s="144"/>
-      <c r="J36" s="143">
+      <c r="I36" s="139"/>
+      <c r="J36" s="138">
         <v>2133.81</v>
       </c>
-      <c r="K36" s="144"/>
-      <c r="L36" s="143">
+      <c r="K36" s="139"/>
+      <c r="L36" s="138">
         <v>1351.66</v>
       </c>
       <c r="M36" s="12"/>
     </row>
     <row r="37" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="118" t="s">
+      <c r="A37" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="114" t="s">
+      <c r="B37" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="115"/>
-      <c r="D37" s="143">
+      <c r="C37" s="110"/>
+      <c r="D37" s="138">
         <v>866.94</v>
       </c>
-      <c r="E37" s="144"/>
-      <c r="F37" s="143">
+      <c r="E37" s="139"/>
+      <c r="F37" s="138">
         <v>886.02</v>
       </c>
-      <c r="G37" s="144"/>
-      <c r="H37" s="143">
+      <c r="G37" s="139"/>
+      <c r="H37" s="138">
         <v>1094.31</v>
       </c>
-      <c r="I37" s="144"/>
-      <c r="J37" s="143">
+      <c r="I37" s="139"/>
+      <c r="J37" s="138">
         <v>966.54</v>
       </c>
-      <c r="K37" s="144"/>
-      <c r="L37" s="143">
+      <c r="K37" s="139"/>
+      <c r="L37" s="138">
         <v>973</v>
       </c>
       <c r="M37" s="12"/>
     </row>
     <row r="38" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="118" t="s">
+      <c r="A38" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="114" t="s">
+      <c r="B38" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="115"/>
-      <c r="D38" s="143">
+      <c r="C38" s="110"/>
+      <c r="D38" s="138">
         <v>3918.78</v>
       </c>
-      <c r="E38" s="144"/>
-      <c r="F38" s="143">
+      <c r="E38" s="139"/>
+      <c r="F38" s="138">
         <v>11205.06</v>
       </c>
-      <c r="G38" s="144"/>
-      <c r="H38" s="143">
+      <c r="G38" s="139"/>
+      <c r="H38" s="138">
         <v>20254.099999999999</v>
       </c>
-      <c r="I38" s="144"/>
-      <c r="J38" s="143">
+      <c r="I38" s="139"/>
+      <c r="J38" s="138">
         <v>15585</v>
       </c>
-      <c r="K38" s="144"/>
-      <c r="L38" s="143">
+      <c r="K38" s="139"/>
+      <c r="L38" s="138">
         <v>6660.58</v>
       </c>
       <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="113" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="114" t="s">
+      <c r="B39" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="115"/>
-      <c r="D39" s="143">
+      <c r="C39" s="110"/>
+      <c r="D39" s="138">
         <v>262.58999999999997</v>
       </c>
-      <c r="E39" s="144"/>
-      <c r="F39" s="143">
+      <c r="E39" s="139"/>
+      <c r="F39" s="138">
         <v>271.82499999999999</v>
       </c>
-      <c r="G39" s="144"/>
-      <c r="H39" s="143">
+      <c r="G39" s="139"/>
+      <c r="H39" s="138">
         <v>576.12</v>
       </c>
-      <c r="I39" s="144"/>
-      <c r="J39" s="143">
+      <c r="I39" s="139"/>
+      <c r="J39" s="138">
         <v>577.02</v>
       </c>
-      <c r="K39" s="144"/>
-      <c r="L39" s="143">
+      <c r="K39" s="139"/>
+      <c r="L39" s="138">
         <v>466.49</v>
       </c>
       <c r="M39" s="12"/>
     </row>
     <row r="40" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="123" t="s">
+      <c r="A40" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="114"/>
-      <c r="C40" s="115"/>
-      <c r="D40" s="128">
+      <c r="B40" s="109"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="123">
         <v>1790</v>
       </c>
-      <c r="E40" s="145"/>
-      <c r="F40" s="128">
+      <c r="E40" s="140"/>
+      <c r="F40" s="123">
         <v>1880</v>
       </c>
-      <c r="G40" s="145"/>
-      <c r="H40" s="128">
+      <c r="G40" s="140"/>
+      <c r="H40" s="123">
         <v>1970</v>
       </c>
-      <c r="I40" s="145"/>
-      <c r="J40" s="128">
+      <c r="I40" s="140"/>
+      <c r="J40" s="123">
         <v>1830</v>
       </c>
-      <c r="K40" s="145"/>
-      <c r="L40" s="128">
+      <c r="K40" s="140"/>
+      <c r="L40" s="123">
         <v>1770</v>
       </c>
       <c r="M40" s="12"/>
     </row>
     <row r="41" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="146" t="s">
+      <c r="A41" s="141" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="114" t="s">
+      <c r="B41" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="115"/>
+      <c r="C41" s="110"/>
       <c r="D41" s="30">
         <v>478000</v>
       </c>
-      <c r="E41" s="147"/>
-      <c r="F41" s="128">
+      <c r="E41" s="142"/>
+      <c r="F41" s="123">
         <v>420000</v>
       </c>
-      <c r="G41" s="147" t="s">
+      <c r="G41" s="142" t="s">
         <v>160</v>
       </c>
       <c r="H41" s="30">
         <v>475000</v>
       </c>
-      <c r="I41" s="147" t="s">
+      <c r="I41" s="142" t="s">
         <v>160</v>
       </c>
       <c r="J41" s="30">
         <v>441000</v>
       </c>
-      <c r="K41" s="147" t="s">
+      <c r="K41" s="142" t="s">
         <v>160</v>
       </c>
       <c r="L41" s="30">
@@ -4729,68 +4716,68 @@
       </c>
     </row>
     <row r="42" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="160" t="s">
+      <c r="A42" s="173" t="s">
         <v>162</v>
       </c>
-      <c r="B42" s="160"/>
-      <c r="C42" s="160"/>
-      <c r="D42" s="160"/>
-      <c r="E42" s="160"/>
-      <c r="F42" s="160"/>
-      <c r="G42" s="160"/>
-      <c r="H42" s="160"/>
-      <c r="I42" s="160"/>
-      <c r="J42" s="160"/>
-      <c r="K42" s="160"/>
-      <c r="L42" s="160"/>
+      <c r="B42" s="173"/>
+      <c r="C42" s="173"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="173"/>
+      <c r="F42" s="173"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="173"/>
+      <c r="I42" s="173"/>
+      <c r="J42" s="173"/>
+      <c r="K42" s="173"/>
+      <c r="L42" s="173"/>
     </row>
     <row r="43" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="161" t="s">
+      <c r="A43" s="174" t="s">
         <v>182</v>
       </c>
-      <c r="B43" s="161"/>
-      <c r="C43" s="161"/>
-      <c r="D43" s="161"/>
-      <c r="E43" s="161"/>
-      <c r="F43" s="161"/>
-      <c r="G43" s="161"/>
-      <c r="H43" s="161"/>
-      <c r="I43" s="161"/>
-      <c r="J43" s="161"/>
-      <c r="K43" s="161"/>
-      <c r="L43" s="161"/>
+      <c r="B43" s="174"/>
+      <c r="C43" s="174"/>
+      <c r="D43" s="174"/>
+      <c r="E43" s="174"/>
+      <c r="F43" s="174"/>
+      <c r="G43" s="174"/>
+      <c r="H43" s="174"/>
+      <c r="I43" s="174"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
+      <c r="L43" s="174"/>
     </row>
     <row r="44" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="156" t="s">
+      <c r="A44" s="169" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="161"/>
-      <c r="C44" s="161"/>
-      <c r="D44" s="161"/>
-      <c r="E44" s="161"/>
-      <c r="F44" s="161"/>
-      <c r="G44" s="161"/>
-      <c r="H44" s="161"/>
-      <c r="I44" s="161"/>
-      <c r="J44" s="161"/>
-      <c r="K44" s="161"/>
-      <c r="L44" s="161"/>
+      <c r="B44" s="174"/>
+      <c r="C44" s="174"/>
+      <c r="D44" s="174"/>
+      <c r="E44" s="174"/>
+      <c r="F44" s="174"/>
+      <c r="G44" s="174"/>
+      <c r="H44" s="174"/>
+      <c r="I44" s="174"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
+      <c r="L44" s="174"/>
     </row>
     <row r="45" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="154" t="s">
+      <c r="A45" s="167" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="155"/>
-      <c r="C45" s="155"/>
-      <c r="D45" s="155"/>
-      <c r="E45" s="155"/>
-      <c r="F45" s="155"/>
-      <c r="G45" s="155"/>
-      <c r="H45" s="155"/>
-      <c r="I45" s="155"/>
-      <c r="J45" s="155"/>
-      <c r="K45" s="155"/>
-      <c r="L45" s="155"/>
+      <c r="B45" s="168"/>
+      <c r="C45" s="168"/>
+      <c r="D45" s="168"/>
+      <c r="E45" s="168"/>
+      <c r="F45" s="168"/>
+      <c r="G45" s="168"/>
+      <c r="H45" s="168"/>
+      <c r="I45" s="168"/>
+      <c r="J45" s="168"/>
+      <c r="K45" s="168"/>
+      <c r="L45" s="168"/>
       <c r="M45" s="101"/>
       <c r="N45" s="101"/>
       <c r="O45" s="101"/>
@@ -4802,59 +4789,59 @@
       <c r="U45" s="101"/>
     </row>
     <row r="46" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="156" t="s">
+      <c r="A46" s="169" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="154"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="154"/>
-      <c r="E46" s="154"/>
-      <c r="F46" s="154"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="154"/>
-      <c r="I46" s="154"/>
-      <c r="J46" s="154"/>
-      <c r="K46" s="154"/>
-      <c r="L46" s="154"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A47" s="156" t="s">
+      <c r="B46" s="167"/>
+      <c r="C46" s="167"/>
+      <c r="D46" s="167"/>
+      <c r="E46" s="167"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
+      <c r="J46" s="167"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="167"/>
+    </row>
+    <row r="47" spans="1:21" ht="12.6" x14ac:dyDescent="0.2">
+      <c r="A47" s="169" t="s">
         <v>110</v>
       </c>
-      <c r="B47" s="154"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="154"/>
-      <c r="E47" s="154"/>
-      <c r="F47" s="154"/>
-      <c r="G47" s="154"/>
-      <c r="H47" s="154"/>
-      <c r="I47" s="154"/>
-      <c r="J47" s="154"/>
-      <c r="K47" s="154"/>
-      <c r="L47" s="154"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A48" s="157" t="s">
+      <c r="B47" s="167"/>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167"/>
+      <c r="E47" s="167"/>
+      <c r="F47" s="167"/>
+      <c r="G47" s="167"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="167"/>
+      <c r="K47" s="167"/>
+      <c r="L47" s="167"/>
+    </row>
+    <row r="48" spans="1:21" ht="12.6" x14ac:dyDescent="0.2">
+      <c r="A48" s="170" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="157"/>
-      <c r="C48" s="157"/>
-      <c r="D48" s="157"/>
-      <c r="E48" s="157"/>
-      <c r="F48" s="157"/>
-      <c r="G48" s="157"/>
-      <c r="H48" s="157"/>
-      <c r="I48" s="157"/>
-      <c r="J48" s="157"/>
-      <c r="K48" s="157"/>
-      <c r="L48" s="157"/>
+      <c r="B48" s="170"/>
+      <c r="C48" s="170"/>
+      <c r="D48" s="170"/>
+      <c r="E48" s="170"/>
+      <c r="F48" s="170"/>
+      <c r="G48" s="170"/>
+      <c r="H48" s="170"/>
+      <c r="I48" s="170"/>
+      <c r="J48" s="170"/>
+      <c r="K48" s="170"/>
+      <c r="L48" s="170"/>
     </row>
     <row r="49" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D49" s="13"/>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
-      <c r="H49" s="148"/>
+      <c r="H49" s="143"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="K49" s="13"/>
@@ -4959,7 +4946,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6378C168-5296-4F8F-B2A6-E612AE97E0AF}">
   <dimension ref="A1:Y89"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" style="26" customWidth="1"/>
     <col min="2" max="2" width="1.83203125" style="26" customWidth="1"/>
@@ -4987,110 +4974,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="162"/>
-      <c r="S1" s="162"/>
-      <c r="T1" s="162"/>
-      <c r="U1" s="162"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
+      <c r="N1" s="175"/>
+      <c r="O1" s="175"/>
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="175"/>
+      <c r="S1" s="175"/>
+      <c r="T1" s="175"/>
+      <c r="U1" s="175"/>
     </row>
     <row r="2" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="175" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="162"/>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
+      <c r="K2" s="175"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="175"/>
+      <c r="Q2" s="175"/>
+      <c r="R2" s="175"/>
+      <c r="S2" s="175"/>
+      <c r="T2" s="175"/>
+      <c r="U2" s="175"/>
     </row>
     <row r="3" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="163"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
-      <c r="P3" s="163"/>
-      <c r="Q3" s="163"/>
-      <c r="R3" s="163"/>
-      <c r="S3" s="163"/>
-      <c r="T3" s="163"/>
-      <c r="U3" s="163"/>
+      <c r="A3" s="176"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="176"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="176"/>
+      <c r="N3" s="176"/>
+      <c r="O3" s="176"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="176"/>
+      <c r="S3" s="176"/>
+      <c r="T3" s="176"/>
+      <c r="U3" s="176"/>
     </row>
     <row r="4" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="71"/>
       <c r="B4" s="27"/>
-      <c r="C4" s="164" t="s">
+      <c r="C4" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
+      <c r="D4" s="177"/>
+      <c r="E4" s="177"/>
       <c r="F4" s="71"/>
-      <c r="G4" s="164" t="s">
+      <c r="G4" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="177"/>
       <c r="J4" s="71"/>
-      <c r="K4" s="164" t="s">
+      <c r="K4" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="164"/>
-      <c r="M4" s="164"/>
+      <c r="L4" s="177"/>
+      <c r="M4" s="177"/>
       <c r="N4" s="71"/>
-      <c r="O4" s="164" t="s">
+      <c r="O4" s="177" t="s">
         <v>96</v>
       </c>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
+      <c r="P4" s="177"/>
+      <c r="Q4" s="177"/>
       <c r="R4" s="71"/>
-      <c r="S4" s="164" t="s">
+      <c r="S4" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
+      <c r="T4" s="177"/>
+      <c r="U4" s="177"/>
     </row>
     <row r="5" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="71"/>
@@ -6487,152 +6474,152 @@
       <c r="Y36" s="28"/>
     </row>
     <row r="37" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="165" t="s">
+      <c r="A37" s="178" t="s">
         <v>161</v>
       </c>
-      <c r="B37" s="165"/>
-      <c r="C37" s="165"/>
-      <c r="D37" s="165"/>
-      <c r="E37" s="165"/>
-      <c r="F37" s="166"/>
-      <c r="G37" s="166"/>
-      <c r="H37" s="166"/>
-      <c r="I37" s="166"/>
-      <c r="J37" s="166"/>
-      <c r="K37" s="166"/>
-      <c r="L37" s="167"/>
-      <c r="M37" s="167"/>
-      <c r="N37" s="167"/>
-      <c r="O37" s="167"/>
-      <c r="P37" s="167"/>
-      <c r="Q37" s="167"/>
-      <c r="R37" s="167"/>
-      <c r="S37" s="167"/>
-      <c r="T37" s="167"/>
-      <c r="U37" s="167"/>
+      <c r="B37" s="178"/>
+      <c r="C37" s="178"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="179"/>
+      <c r="I37" s="179"/>
+      <c r="J37" s="179"/>
+      <c r="K37" s="179"/>
+      <c r="L37" s="180"/>
+      <c r="M37" s="180"/>
+      <c r="N37" s="180"/>
+      <c r="O37" s="180"/>
+      <c r="P37" s="180"/>
+      <c r="Q37" s="180"/>
+      <c r="R37" s="180"/>
+      <c r="S37" s="180"/>
+      <c r="T37" s="180"/>
+      <c r="U37" s="180"/>
     </row>
     <row r="38" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="161" t="s">
+      <c r="A38" s="174" t="s">
         <v>183</v>
       </c>
-      <c r="B38" s="161"/>
-      <c r="C38" s="161"/>
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="161"/>
-      <c r="L38" s="161"/>
-      <c r="M38" s="161"/>
-      <c r="N38" s="161"/>
-      <c r="O38" s="161"/>
-      <c r="P38" s="161"/>
-      <c r="Q38" s="161"/>
-      <c r="R38" s="161"/>
-      <c r="S38" s="161"/>
-      <c r="T38" s="161"/>
-      <c r="U38" s="161"/>
+      <c r="B38" s="174"/>
+      <c r="C38" s="174"/>
+      <c r="D38" s="174"/>
+      <c r="E38" s="174"/>
+      <c r="F38" s="174"/>
+      <c r="G38" s="174"/>
+      <c r="H38" s="174"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="174"/>
+      <c r="K38" s="174"/>
+      <c r="L38" s="174"/>
+      <c r="M38" s="174"/>
+      <c r="N38" s="174"/>
+      <c r="O38" s="174"/>
+      <c r="P38" s="174"/>
+      <c r="Q38" s="174"/>
+      <c r="R38" s="174"/>
+      <c r="S38" s="174"/>
+      <c r="T38" s="174"/>
+      <c r="U38" s="174"/>
     </row>
     <row r="39" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="168" t="s">
+      <c r="A39" s="181" t="s">
         <v>178</v>
       </c>
-      <c r="B39" s="168"/>
-      <c r="C39" s="169"/>
-      <c r="D39" s="169"/>
-      <c r="E39" s="169"/>
-      <c r="F39" s="169"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="169"/>
-      <c r="I39" s="169"/>
-      <c r="J39" s="169"/>
-      <c r="K39" s="169"/>
-      <c r="L39" s="169"/>
-      <c r="M39" s="169"/>
-      <c r="N39" s="169"/>
-      <c r="O39" s="169"/>
-      <c r="P39" s="169"/>
-      <c r="Q39" s="169"/>
-      <c r="R39" s="169"/>
-      <c r="S39" s="169"/>
-      <c r="T39" s="169"/>
-      <c r="U39" s="169"/>
+      <c r="B39" s="181"/>
+      <c r="C39" s="182"/>
+      <c r="D39" s="182"/>
+      <c r="E39" s="182"/>
+      <c r="F39" s="182"/>
+      <c r="G39" s="182"/>
+      <c r="H39" s="182"/>
+      <c r="I39" s="182"/>
+      <c r="J39" s="182"/>
+      <c r="K39" s="182"/>
+      <c r="L39" s="182"/>
+      <c r="M39" s="182"/>
+      <c r="N39" s="182"/>
+      <c r="O39" s="182"/>
+      <c r="P39" s="182"/>
+      <c r="Q39" s="182"/>
+      <c r="R39" s="182"/>
+      <c r="S39" s="182"/>
+      <c r="T39" s="182"/>
+      <c r="U39" s="182"/>
     </row>
     <row r="40" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="154" t="s">
+      <c r="A40" s="167" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="154"/>
-      <c r="C40" s="154"/>
-      <c r="D40" s="154"/>
-      <c r="E40" s="154"/>
-      <c r="F40" s="154"/>
-      <c r="G40" s="154"/>
-      <c r="H40" s="154"/>
-      <c r="I40" s="154"/>
-      <c r="J40" s="154"/>
-      <c r="K40" s="154"/>
-      <c r="L40" s="154"/>
-      <c r="M40" s="154"/>
-      <c r="N40" s="154"/>
-      <c r="O40" s="154"/>
-      <c r="P40" s="154"/>
-      <c r="Q40" s="154"/>
-      <c r="R40" s="154"/>
-      <c r="S40" s="154"/>
-      <c r="T40" s="154"/>
-      <c r="U40" s="154"/>
+      <c r="B40" s="167"/>
+      <c r="C40" s="167"/>
+      <c r="D40" s="167"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="167"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
+      <c r="J40" s="167"/>
+      <c r="K40" s="167"/>
+      <c r="L40" s="167"/>
+      <c r="M40" s="167"/>
+      <c r="N40" s="167"/>
+      <c r="O40" s="167"/>
+      <c r="P40" s="167"/>
+      <c r="Q40" s="167"/>
+      <c r="R40" s="167"/>
+      <c r="S40" s="167"/>
+      <c r="T40" s="167"/>
+      <c r="U40" s="167"/>
     </row>
     <row r="41" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="154"/>
-      <c r="B41" s="154"/>
-      <c r="C41" s="154"/>
-      <c r="D41" s="154"/>
-      <c r="E41" s="154"/>
-      <c r="F41" s="154"/>
-      <c r="G41" s="154"/>
-      <c r="H41" s="154"/>
-      <c r="I41" s="154"/>
-      <c r="J41" s="154"/>
-      <c r="K41" s="154"/>
-      <c r="L41" s="154"/>
-      <c r="M41" s="154"/>
-      <c r="N41" s="154"/>
-      <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
-      <c r="Q41" s="154"/>
-      <c r="R41" s="154"/>
-      <c r="S41" s="154"/>
-      <c r="T41" s="154"/>
-      <c r="U41" s="154"/>
+      <c r="A41" s="167"/>
+      <c r="B41" s="167"/>
+      <c r="C41" s="167"/>
+      <c r="D41" s="167"/>
+      <c r="E41" s="167"/>
+      <c r="F41" s="167"/>
+      <c r="G41" s="167"/>
+      <c r="H41" s="167"/>
+      <c r="I41" s="167"/>
+      <c r="J41" s="167"/>
+      <c r="K41" s="167"/>
+      <c r="L41" s="167"/>
+      <c r="M41" s="167"/>
+      <c r="N41" s="167"/>
+      <c r="O41" s="167"/>
+      <c r="P41" s="167"/>
+      <c r="Q41" s="167"/>
+      <c r="R41" s="167"/>
+      <c r="S41" s="167"/>
+      <c r="T41" s="167"/>
+      <c r="U41" s="167"/>
     </row>
     <row r="42" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="156" t="s">
+      <c r="A42" s="169" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="156"/>
-      <c r="C42" s="156"/>
-      <c r="D42" s="156"/>
-      <c r="E42" s="156"/>
-      <c r="F42" s="156"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="156"/>
-      <c r="I42" s="156"/>
-      <c r="J42" s="156"/>
-      <c r="K42" s="156"/>
-      <c r="L42" s="156"/>
-      <c r="M42" s="156"/>
-      <c r="N42" s="156"/>
-      <c r="O42" s="156"/>
-      <c r="P42" s="156"/>
-      <c r="Q42" s="156"/>
-      <c r="R42" s="156"/>
-      <c r="S42" s="156"/>
-      <c r="T42" s="156"/>
-      <c r="U42" s="156"/>
+      <c r="B42" s="169"/>
+      <c r="C42" s="169"/>
+      <c r="D42" s="169"/>
+      <c r="E42" s="169"/>
+      <c r="F42" s="169"/>
+      <c r="G42" s="169"/>
+      <c r="H42" s="169"/>
+      <c r="I42" s="169"/>
+      <c r="J42" s="169"/>
+      <c r="K42" s="169"/>
+      <c r="L42" s="169"/>
+      <c r="M42" s="169"/>
+      <c r="N42" s="169"/>
+      <c r="O42" s="169"/>
+      <c r="P42" s="169"/>
+      <c r="Q42" s="169"/>
+      <c r="R42" s="169"/>
+      <c r="S42" s="169"/>
+      <c r="T42" s="169"/>
+      <c r="U42" s="169"/>
     </row>
     <row r="43" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C43" s="28"/>
@@ -6678,7 +6665,7 @@
     </row>
     <row r="82" spans="3:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="83" spans="3:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:24" ht="10.199999999999999" x14ac:dyDescent="0.2">
       <c r="C86" s="34"/>
       <c r="D86" s="34"/>
       <c r="E86" s="34"/>
@@ -6697,7 +6684,7 @@
       <c r="R86" s="34"/>
       <c r="S86" s="34"/>
     </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:24" ht="10.199999999999999" x14ac:dyDescent="0.2">
       <c r="C87" s="34"/>
       <c r="D87" s="34"/>
       <c r="E87" s="34"/>
@@ -6718,7 +6705,7 @@
       <c r="V87" s="28"/>
       <c r="X87" s="28"/>
     </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:24" ht="10.199999999999999" x14ac:dyDescent="0.2">
       <c r="C88" s="34"/>
       <c r="D88" s="34"/>
       <c r="E88" s="34"/>
@@ -6737,7 +6724,7 @@
       <c r="R88" s="34"/>
       <c r="S88" s="34"/>
     </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:24" ht="10.199999999999999" x14ac:dyDescent="0.2">
       <c r="C89" s="34"/>
       <c r="D89" s="34"/>
       <c r="E89" s="34"/>
@@ -6782,7 +6769,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD5EF06-5CC4-4900-82A4-286190E16ABD}">
   <dimension ref="A1:AA107"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" style="26" customWidth="1"/>
     <col min="2" max="2" width="1.83203125" style="26" customWidth="1"/>
@@ -6815,131 +6802,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="162"/>
-      <c r="S1" s="162"/>
-      <c r="T1" s="162"/>
-      <c r="U1" s="162"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
-      <c r="Z1" s="170"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
+      <c r="N1" s="175"/>
+      <c r="O1" s="175"/>
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="175"/>
+      <c r="S1" s="175"/>
+      <c r="T1" s="175"/>
+      <c r="U1" s="175"/>
+      <c r="V1" s="183"/>
+      <c r="W1" s="183"/>
+      <c r="X1" s="183"/>
+      <c r="Y1" s="183"/>
+      <c r="Z1" s="183"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="175" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="162"/>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
-      <c r="V2" s="170"/>
-      <c r="W2" s="170"/>
-      <c r="X2" s="170"/>
-      <c r="Y2" s="170"/>
-      <c r="Z2" s="170"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
+      <c r="K2" s="175"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="175"/>
+      <c r="Q2" s="175"/>
+      <c r="R2" s="175"/>
+      <c r="S2" s="175"/>
+      <c r="T2" s="175"/>
+      <c r="U2" s="175"/>
+      <c r="V2" s="183"/>
+      <c r="W2" s="183"/>
+      <c r="X2" s="183"/>
+      <c r="Y2" s="183"/>
+      <c r="Z2" s="183"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="162"/>
-      <c r="B3" s="162"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="162"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="162"/>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="170"/>
-      <c r="Y3" s="170"/>
-      <c r="Z3" s="170"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
+      <c r="L3" s="175"/>
+      <c r="M3" s="175"/>
+      <c r="N3" s="175"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="175"/>
+      <c r="Q3" s="175"/>
+      <c r="R3" s="175"/>
+      <c r="S3" s="175"/>
+      <c r="T3" s="175"/>
+      <c r="U3" s="175"/>
+      <c r="V3" s="183"/>
+      <c r="W3" s="183"/>
+      <c r="X3" s="183"/>
+      <c r="Y3" s="183"/>
+      <c r="Z3" s="183"/>
     </row>
     <row r="4" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="74"/>
       <c r="B4" s="74"/>
-      <c r="C4" s="171" t="s">
+      <c r="C4" s="184" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="171"/>
-      <c r="E4" s="171"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
       <c r="F4" s="74"/>
-      <c r="G4" s="171" t="s">
+      <c r="G4" s="184" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="171"/>
-      <c r="I4" s="171"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="171" t="s">
+      <c r="K4" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="171"/>
-      <c r="M4" s="171"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
       <c r="N4" s="74"/>
-      <c r="O4" s="171" t="s">
+      <c r="O4" s="184" t="s">
         <v>71</v>
       </c>
-      <c r="P4" s="171"/>
-      <c r="Q4" s="171"/>
+      <c r="P4" s="184"/>
+      <c r="Q4" s="184"/>
       <c r="R4" s="74"/>
-      <c r="S4" s="171" t="s">
+      <c r="S4" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="T4" s="171"/>
-      <c r="U4" s="171"/>
+      <c r="T4" s="184"/>
+      <c r="U4" s="184"/>
       <c r="V4" s="74"/>
-      <c r="W4" s="164" t="s">
+      <c r="W4" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="172"/>
-      <c r="Y4" s="172"/>
+      <c r="X4" s="185"/>
+      <c r="Y4" s="185"/>
       <c r="Z4" s="74"/>
     </row>
     <row r="5" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8842,212 +8829,212 @@
       <c r="AA41" s="62"/>
     </row>
     <row r="42" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="173" t="s">
+      <c r="A42" s="186" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="174"/>
-      <c r="C42" s="174"/>
-      <c r="D42" s="174"/>
-      <c r="E42" s="174"/>
-      <c r="F42" s="174"/>
-      <c r="G42" s="174"/>
-      <c r="H42" s="174"/>
-      <c r="I42" s="174"/>
-      <c r="J42" s="174"/>
-      <c r="K42" s="174"/>
-      <c r="L42" s="174"/>
-      <c r="M42" s="174"/>
-      <c r="N42" s="174"/>
-      <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
-      <c r="Q42" s="174"/>
-      <c r="R42" s="174"/>
-      <c r="S42" s="174"/>
-      <c r="T42" s="174"/>
-      <c r="U42" s="174"/>
-      <c r="V42" s="155"/>
-      <c r="W42" s="155"/>
-      <c r="X42" s="155"/>
-      <c r="Y42" s="155"/>
-      <c r="Z42" s="155"/>
+      <c r="B42" s="187"/>
+      <c r="C42" s="187"/>
+      <c r="D42" s="187"/>
+      <c r="E42" s="187"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="187"/>
+      <c r="I42" s="187"/>
+      <c r="J42" s="187"/>
+      <c r="K42" s="187"/>
+      <c r="L42" s="187"/>
+      <c r="M42" s="187"/>
+      <c r="N42" s="187"/>
+      <c r="O42" s="187"/>
+      <c r="P42" s="187"/>
+      <c r="Q42" s="187"/>
+      <c r="R42" s="187"/>
+      <c r="S42" s="187"/>
+      <c r="T42" s="187"/>
+      <c r="U42" s="187"/>
+      <c r="V42" s="168"/>
+      <c r="W42" s="168"/>
+      <c r="X42" s="168"/>
+      <c r="Y42" s="168"/>
+      <c r="Z42" s="168"/>
     </row>
     <row r="43" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="161" t="s">
+      <c r="A43" s="174" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="161"/>
-      <c r="C43" s="161"/>
-      <c r="D43" s="161"/>
-      <c r="E43" s="161"/>
-      <c r="F43" s="161"/>
-      <c r="G43" s="161"/>
-      <c r="H43" s="161"/>
-      <c r="I43" s="161"/>
-      <c r="J43" s="161"/>
-      <c r="K43" s="161"/>
-      <c r="L43" s="161"/>
-      <c r="M43" s="161"/>
-      <c r="N43" s="161"/>
-      <c r="O43" s="161"/>
-      <c r="P43" s="161"/>
-      <c r="Q43" s="161"/>
-      <c r="R43" s="161"/>
-      <c r="S43" s="161"/>
-      <c r="T43" s="161"/>
-      <c r="U43" s="161"/>
-      <c r="V43" s="155"/>
-      <c r="W43" s="155"/>
-      <c r="X43" s="155"/>
-      <c r="Y43" s="155"/>
-      <c r="Z43" s="155"/>
+      <c r="B43" s="174"/>
+      <c r="C43" s="174"/>
+      <c r="D43" s="174"/>
+      <c r="E43" s="174"/>
+      <c r="F43" s="174"/>
+      <c r="G43" s="174"/>
+      <c r="H43" s="174"/>
+      <c r="I43" s="174"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
+      <c r="L43" s="174"/>
+      <c r="M43" s="174"/>
+      <c r="N43" s="174"/>
+      <c r="O43" s="174"/>
+      <c r="P43" s="174"/>
+      <c r="Q43" s="174"/>
+      <c r="R43" s="174"/>
+      <c r="S43" s="174"/>
+      <c r="T43" s="174"/>
+      <c r="U43" s="174"/>
+      <c r="V43" s="168"/>
+      <c r="W43" s="168"/>
+      <c r="X43" s="168"/>
+      <c r="Y43" s="168"/>
+      <c r="Z43" s="168"/>
     </row>
     <row r="44" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="154" t="s">
+      <c r="A44" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="B44" s="154"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="154"/>
-      <c r="E44" s="154"/>
-      <c r="F44" s="154"/>
-      <c r="G44" s="154"/>
-      <c r="H44" s="154"/>
-      <c r="I44" s="154"/>
-      <c r="J44" s="154"/>
-      <c r="K44" s="154"/>
-      <c r="L44" s="154"/>
-      <c r="M44" s="154"/>
-      <c r="N44" s="154"/>
-      <c r="O44" s="154"/>
-      <c r="P44" s="154"/>
-      <c r="Q44" s="154"/>
-      <c r="R44" s="154"/>
-      <c r="S44" s="154"/>
-      <c r="T44" s="154"/>
-      <c r="U44" s="154"/>
-      <c r="V44" s="155"/>
-      <c r="W44" s="155"/>
-      <c r="X44" s="155"/>
-      <c r="Y44" s="155"/>
-      <c r="Z44" s="155"/>
+      <c r="B44" s="167"/>
+      <c r="C44" s="167"/>
+      <c r="D44" s="167"/>
+      <c r="E44" s="167"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="167"/>
+      <c r="H44" s="167"/>
+      <c r="I44" s="167"/>
+      <c r="J44" s="167"/>
+      <c r="K44" s="167"/>
+      <c r="L44" s="167"/>
+      <c r="M44" s="167"/>
+      <c r="N44" s="167"/>
+      <c r="O44" s="167"/>
+      <c r="P44" s="167"/>
+      <c r="Q44" s="167"/>
+      <c r="R44" s="167"/>
+      <c r="S44" s="167"/>
+      <c r="T44" s="167"/>
+      <c r="U44" s="167"/>
+      <c r="V44" s="168"/>
+      <c r="W44" s="168"/>
+      <c r="X44" s="168"/>
+      <c r="Y44" s="168"/>
+      <c r="Z44" s="168"/>
     </row>
     <row r="45" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="168" t="s">
+      <c r="A45" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="B45" s="168"/>
-      <c r="C45" s="169"/>
-      <c r="D45" s="169"/>
-      <c r="E45" s="169"/>
-      <c r="F45" s="169"/>
-      <c r="G45" s="169"/>
-      <c r="H45" s="169"/>
-      <c r="I45" s="169"/>
-      <c r="J45" s="169"/>
-      <c r="K45" s="169"/>
-      <c r="L45" s="169"/>
-      <c r="M45" s="169"/>
-      <c r="N45" s="169"/>
-      <c r="O45" s="169"/>
-      <c r="P45" s="169"/>
-      <c r="Q45" s="169"/>
-      <c r="R45" s="169"/>
-      <c r="S45" s="169"/>
-      <c r="T45" s="169"/>
-      <c r="U45" s="169"/>
-      <c r="V45" s="175"/>
-      <c r="W45" s="175"/>
-      <c r="X45" s="175"/>
-      <c r="Y45" s="175"/>
-      <c r="Z45" s="175"/>
+      <c r="B45" s="181"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="182"/>
+      <c r="F45" s="182"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="182"/>
+      <c r="I45" s="182"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="182"/>
+      <c r="L45" s="182"/>
+      <c r="M45" s="182"/>
+      <c r="N45" s="182"/>
+      <c r="O45" s="182"/>
+      <c r="P45" s="182"/>
+      <c r="Q45" s="182"/>
+      <c r="R45" s="182"/>
+      <c r="S45" s="182"/>
+      <c r="T45" s="182"/>
+      <c r="U45" s="182"/>
+      <c r="V45" s="188"/>
+      <c r="W45" s="188"/>
+      <c r="X45" s="188"/>
+      <c r="Y45" s="188"/>
+      <c r="Z45" s="188"/>
     </row>
     <row r="46" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="154" t="s">
+      <c r="A46" s="167" t="s">
         <v>177</v>
       </c>
-      <c r="B46" s="154"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="154"/>
-      <c r="E46" s="154"/>
-      <c r="F46" s="154"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="154"/>
-      <c r="I46" s="154"/>
-      <c r="J46" s="154"/>
-      <c r="K46" s="154"/>
-      <c r="L46" s="154"/>
-      <c r="M46" s="154"/>
-      <c r="N46" s="154"/>
-      <c r="O46" s="154"/>
-      <c r="P46" s="154"/>
-      <c r="Q46" s="154"/>
-      <c r="R46" s="154"/>
-      <c r="S46" s="154"/>
-      <c r="T46" s="154"/>
-      <c r="U46" s="154"/>
-      <c r="V46" s="155"/>
-      <c r="W46" s="155"/>
-      <c r="X46" s="155"/>
-      <c r="Y46" s="155"/>
-      <c r="Z46" s="155"/>
+      <c r="B46" s="167"/>
+      <c r="C46" s="167"/>
+      <c r="D46" s="167"/>
+      <c r="E46" s="167"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
+      <c r="J46" s="167"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="167"/>
+      <c r="M46" s="167"/>
+      <c r="N46" s="167"/>
+      <c r="O46" s="167"/>
+      <c r="P46" s="167"/>
+      <c r="Q46" s="167"/>
+      <c r="R46" s="167"/>
+      <c r="S46" s="167"/>
+      <c r="T46" s="167"/>
+      <c r="U46" s="167"/>
+      <c r="V46" s="168"/>
+      <c r="W46" s="168"/>
+      <c r="X46" s="168"/>
+      <c r="Y46" s="168"/>
+      <c r="Z46" s="168"/>
     </row>
     <row r="47" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="161"/>
-      <c r="B47" s="154"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="154"/>
-      <c r="E47" s="154"/>
-      <c r="F47" s="154"/>
-      <c r="G47" s="154"/>
-      <c r="H47" s="154"/>
-      <c r="I47" s="154"/>
-      <c r="J47" s="154"/>
-      <c r="K47" s="154"/>
-      <c r="L47" s="154"/>
-      <c r="M47" s="154"/>
-      <c r="N47" s="154"/>
-      <c r="O47" s="154"/>
-      <c r="P47" s="154"/>
-      <c r="Q47" s="154"/>
-      <c r="R47" s="154"/>
-      <c r="S47" s="154"/>
-      <c r="T47" s="154"/>
-      <c r="U47" s="154"/>
-      <c r="V47" s="155"/>
-      <c r="W47" s="155"/>
-      <c r="X47" s="155"/>
-      <c r="Y47" s="155"/>
-      <c r="Z47" s="155"/>
+      <c r="A47" s="174"/>
+      <c r="B47" s="167"/>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167"/>
+      <c r="E47" s="167"/>
+      <c r="F47" s="167"/>
+      <c r="G47" s="167"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="167"/>
+      <c r="K47" s="167"/>
+      <c r="L47" s="167"/>
+      <c r="M47" s="167"/>
+      <c r="N47" s="167"/>
+      <c r="O47" s="167"/>
+      <c r="P47" s="167"/>
+      <c r="Q47" s="167"/>
+      <c r="R47" s="167"/>
+      <c r="S47" s="167"/>
+      <c r="T47" s="167"/>
+      <c r="U47" s="167"/>
+      <c r="V47" s="168"/>
+      <c r="W47" s="168"/>
+      <c r="X47" s="168"/>
+      <c r="Y47" s="168"/>
+      <c r="Z47" s="168"/>
     </row>
     <row r="48" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="156" t="s">
+      <c r="A48" s="169" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="156"/>
-      <c r="C48" s="156"/>
-      <c r="D48" s="156"/>
-      <c r="E48" s="156"/>
-      <c r="F48" s="156"/>
-      <c r="G48" s="156"/>
-      <c r="H48" s="156"/>
-      <c r="I48" s="156"/>
-      <c r="J48" s="156"/>
-      <c r="K48" s="156"/>
-      <c r="L48" s="156"/>
-      <c r="M48" s="156"/>
-      <c r="N48" s="156"/>
-      <c r="O48" s="156"/>
-      <c r="P48" s="156"/>
-      <c r="Q48" s="156"/>
-      <c r="R48" s="156"/>
-      <c r="S48" s="156"/>
-      <c r="T48" s="156"/>
-      <c r="U48" s="156"/>
-      <c r="V48" s="155"/>
-      <c r="W48" s="155"/>
-      <c r="X48" s="155"/>
-      <c r="Y48" s="155"/>
-      <c r="Z48" s="155"/>
+      <c r="B48" s="169"/>
+      <c r="C48" s="169"/>
+      <c r="D48" s="169"/>
+      <c r="E48" s="169"/>
+      <c r="F48" s="169"/>
+      <c r="G48" s="169"/>
+      <c r="H48" s="169"/>
+      <c r="I48" s="169"/>
+      <c r="J48" s="169"/>
+      <c r="K48" s="169"/>
+      <c r="L48" s="169"/>
+      <c r="M48" s="169"/>
+      <c r="N48" s="169"/>
+      <c r="O48" s="169"/>
+      <c r="P48" s="169"/>
+      <c r="Q48" s="169"/>
+      <c r="R48" s="169"/>
+      <c r="S48" s="169"/>
+      <c r="T48" s="169"/>
+      <c r="U48" s="169"/>
+      <c r="V48" s="168"/>
+      <c r="W48" s="168"/>
+      <c r="X48" s="168"/>
+      <c r="Y48" s="168"/>
+      <c r="Z48" s="168"/>
     </row>
     <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="28"/>
@@ -9182,7 +9169,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E51F4D-161A-4D30-AF45-1AA21B68480B}">
   <dimension ref="A1:DJ75"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="26" customWidth="1"/>
     <col min="2" max="2" width="1.83203125" style="26" customWidth="1"/>
@@ -9210,251 +9197,251 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="175" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="162"/>
-      <c r="S1" s="162"/>
-      <c r="T1" s="162"/>
-      <c r="U1" s="162"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
+      <c r="N1" s="175"/>
+      <c r="O1" s="175"/>
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="175"/>
+      <c r="S1" s="175"/>
+      <c r="T1" s="175"/>
+      <c r="U1" s="175"/>
     </row>
     <row r="2" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="162"/>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
+      <c r="K2" s="175"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="175"/>
+      <c r="Q2" s="175"/>
+      <c r="R2" s="175"/>
+      <c r="S2" s="175"/>
+      <c r="T2" s="175"/>
+      <c r="U2" s="175"/>
     </row>
     <row r="3" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="178"/>
-      <c r="B3" s="178"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="178"/>
-      <c r="O3" s="178"/>
-      <c r="P3" s="178"/>
-      <c r="Q3" s="178"/>
-      <c r="R3" s="178"/>
-      <c r="S3" s="178"/>
-      <c r="T3" s="178"/>
-      <c r="U3" s="178"/>
+      <c r="A3" s="191"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="191"/>
+      <c r="K3" s="191"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="191"/>
+      <c r="Q3" s="191"/>
+      <c r="R3" s="191"/>
+      <c r="S3" s="191"/>
+      <c r="T3" s="191"/>
+      <c r="U3" s="191"/>
     </row>
     <row r="4" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="179"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="179" t="s">
+      <c r="K4" s="192" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="179"/>
-      <c r="M4" s="180"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="179"/>
-      <c r="P4" s="179"/>
-      <c r="Q4" s="179"/>
+      <c r="L4" s="192"/>
+      <c r="M4" s="193"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="192"/>
+      <c r="P4" s="192"/>
+      <c r="Q4" s="192"/>
       <c r="R4" s="35"/>
-      <c r="S4" s="181"/>
-      <c r="T4" s="181"/>
-      <c r="U4" s="181"/>
+      <c r="S4" s="194"/>
+      <c r="T4" s="194"/>
+      <c r="U4" s="194"/>
     </row>
     <row r="5" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="105"/>
-      <c r="B5" s="105"/>
-      <c r="C5" s="163" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="176" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="163"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="163" t="s">
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="163" t="s">
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="176" t="s">
         <v>65</v>
       </c>
-      <c r="L5" s="163"/>
-      <c r="M5" s="163"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="176"/>
       <c r="N5" s="25"/>
-      <c r="O5" s="163" t="s">
+      <c r="O5" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="163"/>
-      <c r="Q5" s="163"/>
-      <c r="S5" s="163" t="s">
+      <c r="P5" s="176"/>
+      <c r="Q5" s="176"/>
+      <c r="S5" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="T5" s="182"/>
-      <c r="U5" s="182"/>
+      <c r="T5" s="195"/>
+      <c r="U5" s="195"/>
     </row>
     <row r="6" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="105"/>
-      <c r="B6" s="105"/>
-      <c r="C6" s="103" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="103" t="s">
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="103" t="s">
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="L6" s="103"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="103" t="s">
+      <c r="L6" s="71"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="S6" s="103" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="S6" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
     </row>
     <row r="7" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="105"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="103" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103" t="s">
+      <c r="D7" s="71"/>
+      <c r="E7" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="105"/>
-      <c r="G7" s="103" t="s">
+      <c r="F7" s="27"/>
+      <c r="G7" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103" t="s">
+      <c r="H7" s="71"/>
+      <c r="I7" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="103" t="s">
+      <c r="J7" s="27"/>
+      <c r="K7" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103" t="s">
+      <c r="L7" s="71"/>
+      <c r="M7" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="N7" s="103"/>
-      <c r="O7" s="103" t="s">
+      <c r="N7" s="71"/>
+      <c r="O7" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103" t="s">
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71" t="s">
         <v>2</v>
       </c>
       <c r="R7" s="14"/>
-      <c r="S7" s="102" t="s">
+      <c r="S7" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103" t="s">
+      <c r="T7" s="71"/>
+      <c r="U7" s="71" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="72" t="s">
         <v>89</v>
       </c>
       <c r="B8" s="21"/>
-      <c r="C8" s="104" t="s">
+      <c r="C8" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104" t="s">
+      <c r="D8" s="72"/>
+      <c r="E8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104" t="s">
+      <c r="F8" s="72"/>
+      <c r="G8" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104" t="s">
+      <c r="H8" s="72"/>
+      <c r="I8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104" t="s">
+      <c r="J8" s="72"/>
+      <c r="K8" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104" t="s">
+      <c r="L8" s="72"/>
+      <c r="M8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104" t="s">
+      <c r="N8" s="72"/>
+      <c r="O8" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="P8" s="104"/>
-      <c r="Q8" s="104" t="s">
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="S8" s="104" t="s">
+      <c r="S8" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="T8" s="104"/>
-      <c r="U8" s="104" t="s">
+      <c r="T8" s="72"/>
+      <c r="U8" s="72" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9561,7 +9548,7 @@
       <c r="K11" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L11" s="107"/>
+      <c r="L11" s="73"/>
       <c r="M11" s="56" t="s">
         <v>103</v>
       </c>
@@ -9569,14 +9556,14 @@
       <c r="O11" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P11" s="107"/>
+      <c r="P11" s="73"/>
       <c r="Q11" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S11" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T11" s="107"/>
+      <c r="T11" s="73"/>
       <c r="U11" s="56" t="s">
         <v>103</v>
       </c>
@@ -9617,7 +9604,7 @@
       <c r="S12" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T12" s="107"/>
+      <c r="T12" s="73"/>
       <c r="U12" s="56" t="s">
         <v>103</v>
       </c>
@@ -9631,7 +9618,7 @@
       <c r="C13" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="107"/>
+      <c r="D13" s="73"/>
       <c r="E13" s="56" t="s">
         <v>103</v>
       </c>
@@ -9739,7 +9726,7 @@
       <c r="S15" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T15" s="107"/>
+      <c r="T15" s="73"/>
       <c r="U15" s="56" t="s">
         <v>103</v>
       </c>
@@ -9820,7 +9807,7 @@
       <c r="S17" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T17" s="107"/>
+      <c r="T17" s="73"/>
       <c r="U17" s="56" t="s">
         <v>103</v>
       </c>
@@ -9848,7 +9835,7 @@
       <c r="K18" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="107"/>
+      <c r="L18" s="73"/>
       <c r="M18" s="56" t="s">
         <v>103</v>
       </c>
@@ -9856,14 +9843,14 @@
       <c r="O18" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="107"/>
+      <c r="P18" s="73"/>
       <c r="Q18" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S18" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T18" s="107"/>
+      <c r="T18" s="73"/>
       <c r="U18" s="56" t="s">
         <v>103</v>
       </c>
@@ -9898,14 +9885,14 @@
       <c r="O19" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P19" s="107"/>
+      <c r="P19" s="73"/>
       <c r="Q19" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S19" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T19" s="107"/>
+      <c r="T19" s="73"/>
       <c r="U19" s="56" t="s">
         <v>103</v>
       </c>
@@ -9933,7 +9920,7 @@
       <c r="K20" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L20" s="107"/>
+      <c r="L20" s="73"/>
       <c r="M20" s="56" t="s">
         <v>103</v>
       </c>
@@ -9941,7 +9928,7 @@
       <c r="O20" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P20" s="107"/>
+      <c r="P20" s="73"/>
       <c r="Q20" s="56" t="s">
         <v>103</v>
       </c>
@@ -9975,7 +9962,7 @@
       <c r="K21" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L21" s="107"/>
+      <c r="L21" s="73"/>
       <c r="M21" s="56" t="s">
         <v>103</v>
       </c>
@@ -9983,14 +9970,14 @@
       <c r="O21" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P21" s="107"/>
+      <c r="P21" s="73"/>
       <c r="Q21" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S21" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T21" s="107"/>
+      <c r="T21" s="73"/>
       <c r="U21" s="56" t="s">
         <v>103</v>
       </c>
@@ -10018,7 +10005,7 @@
       <c r="K22" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L22" s="107"/>
+      <c r="L22" s="73"/>
       <c r="M22" s="56" t="s">
         <v>103</v>
       </c>
@@ -10032,7 +10019,7 @@
       <c r="S22" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T22" s="107"/>
+      <c r="T22" s="73"/>
       <c r="U22" s="56" t="s">
         <v>103</v>
       </c>
@@ -10213,7 +10200,7 @@
       <c r="G27" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="107"/>
+      <c r="H27" s="73"/>
       <c r="I27" s="56" t="s">
         <v>103</v>
       </c>
@@ -10221,7 +10208,7 @@
       <c r="K27" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L27" s="107"/>
+      <c r="L27" s="73"/>
       <c r="M27" s="56" t="s">
         <v>103</v>
       </c>
@@ -10229,14 +10216,14 @@
       <c r="O27" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P27" s="107"/>
+      <c r="P27" s="73"/>
       <c r="Q27" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S27" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T27" s="107"/>
+      <c r="T27" s="73"/>
       <c r="U27" s="56" t="s">
         <v>103</v>
       </c>
@@ -10271,7 +10258,7 @@
       <c r="O28" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="107"/>
+      <c r="P28" s="73"/>
       <c r="Q28" s="56" t="s">
         <v>103</v>
       </c>
@@ -10305,7 +10292,7 @@
       <c r="K29" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L29" s="107"/>
+      <c r="L29" s="73"/>
       <c r="M29" s="56" t="s">
         <v>103</v>
       </c>
@@ -10319,7 +10306,7 @@
       <c r="S29" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T29" s="107"/>
+      <c r="T29" s="73"/>
       <c r="U29" s="56" t="s">
         <v>103</v>
       </c>
@@ -10440,7 +10427,7 @@
       <c r="S32" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T32" s="107"/>
+      <c r="T32" s="73"/>
       <c r="U32" s="56" t="s">
         <v>103</v>
       </c>
@@ -10454,7 +10441,7 @@
       <c r="C33" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="107"/>
+      <c r="D33" s="73"/>
       <c r="E33" s="56" t="s">
         <v>103</v>
       </c>
@@ -10469,7 +10456,7 @@
       <c r="K33" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L33" s="107"/>
+      <c r="L33" s="73"/>
       <c r="M33" s="56" t="s">
         <v>103</v>
       </c>
@@ -10477,14 +10464,14 @@
       <c r="O33" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P33" s="107"/>
+      <c r="P33" s="73"/>
       <c r="Q33" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S33" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T33" s="107"/>
+      <c r="T33" s="73"/>
       <c r="U33" s="56" t="s">
         <v>103</v>
       </c>
@@ -10519,14 +10506,14 @@
       <c r="O34" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P34" s="107"/>
+      <c r="P34" s="73"/>
       <c r="Q34" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S34" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T34" s="107"/>
+      <c r="T34" s="73"/>
       <c r="U34" s="56" t="s">
         <v>103</v>
       </c>
@@ -10567,7 +10554,7 @@
       <c r="S35" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T35" s="107"/>
+      <c r="T35" s="73"/>
       <c r="U35" s="56" t="s">
         <v>103</v>
       </c>
@@ -10602,7 +10589,7 @@
       <c r="O36" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P36" s="107"/>
+      <c r="P36" s="73"/>
       <c r="Q36" s="56" t="s">
         <v>103</v>
       </c>
@@ -10636,7 +10623,7 @@
       <c r="K37" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L37" s="107"/>
+      <c r="L37" s="73"/>
       <c r="M37" s="56" t="s">
         <v>103</v>
       </c>
@@ -10644,14 +10631,14 @@
       <c r="O37" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P37" s="107"/>
+      <c r="P37" s="73"/>
       <c r="Q37" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S37" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T37" s="107"/>
+      <c r="T37" s="73"/>
       <c r="U37" s="56" t="s">
         <v>103</v>
       </c>
@@ -10679,7 +10666,7 @@
       <c r="K38" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L38" s="107"/>
+      <c r="L38" s="73"/>
       <c r="M38" s="56" t="s">
         <v>103</v>
       </c>
@@ -10687,14 +10674,14 @@
       <c r="O38" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P38" s="107"/>
+      <c r="P38" s="73"/>
       <c r="Q38" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S38" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T38" s="107"/>
+      <c r="T38" s="73"/>
       <c r="U38" s="56" t="s">
         <v>103</v>
       </c>
@@ -10722,7 +10709,7 @@
       <c r="K39" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L39" s="107"/>
+      <c r="L39" s="73"/>
       <c r="M39" s="56" t="s">
         <v>103</v>
       </c>
@@ -10730,7 +10717,7 @@
       <c r="O39" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P39" s="107"/>
+      <c r="P39" s="73"/>
       <c r="Q39" s="56" t="s">
         <v>103</v>
       </c>
@@ -10757,7 +10744,7 @@
       <c r="G40" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H40" s="107"/>
+      <c r="H40" s="73"/>
       <c r="I40" s="56" t="s">
         <v>103</v>
       </c>
@@ -10765,7 +10752,7 @@
       <c r="K40" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L40" s="107"/>
+      <c r="L40" s="73"/>
       <c r="M40" s="56" t="s">
         <v>103</v>
       </c>
@@ -10773,14 +10760,14 @@
       <c r="O40" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P40" s="107"/>
+      <c r="P40" s="73"/>
       <c r="Q40" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S40" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T40" s="107"/>
+      <c r="T40" s="73"/>
       <c r="U40" s="56" t="s">
         <v>103</v>
       </c>
@@ -10808,7 +10795,7 @@
       <c r="K41" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L41" s="107"/>
+      <c r="L41" s="73"/>
       <c r="M41" s="56" t="s">
         <v>103</v>
       </c>
@@ -10816,14 +10803,14 @@
       <c r="O41" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P41" s="107"/>
+      <c r="P41" s="73"/>
       <c r="Q41" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S41" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T41" s="107"/>
+      <c r="T41" s="73"/>
       <c r="U41" s="56" t="s">
         <v>103</v>
       </c>
@@ -10837,7 +10824,7 @@
       <c r="C42" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="107"/>
+      <c r="D42" s="73"/>
       <c r="E42" s="56" t="s">
         <v>103</v>
       </c>
@@ -10859,7 +10846,7 @@
       <c r="O42" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P42" s="107"/>
+      <c r="P42" s="73"/>
       <c r="Q42" s="56" t="s">
         <v>103</v>
       </c>
@@ -10900,7 +10887,7 @@
       <c r="O43" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P43" s="107"/>
+      <c r="P43" s="73"/>
       <c r="Q43" s="56" t="s">
         <v>103</v>
       </c>
@@ -10933,7 +10920,7 @@
       <c r="K44" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L44" s="107"/>
+      <c r="L44" s="73"/>
       <c r="M44" s="56" t="s">
         <v>103</v>
       </c>
@@ -10941,7 +10928,7 @@
       <c r="O44" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P44" s="107"/>
+      <c r="P44" s="73"/>
       <c r="Q44" s="56" t="s">
         <v>103</v>
       </c>
@@ -11021,14 +11008,14 @@
       <c r="O46" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P46" s="107"/>
+      <c r="P46" s="73"/>
       <c r="Q46" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S46" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T46" s="107"/>
+      <c r="T46" s="73"/>
       <c r="U46" s="56" t="s">
         <v>103</v>
       </c>
@@ -11056,7 +11043,7 @@
       <c r="K47" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L47" s="107"/>
+      <c r="L47" s="73"/>
       <c r="M47" s="56" t="s">
         <v>103</v>
       </c>
@@ -11064,14 +11051,14 @@
       <c r="O47" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P47" s="107"/>
+      <c r="P47" s="73"/>
       <c r="Q47" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S47" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T47" s="107"/>
+      <c r="T47" s="73"/>
       <c r="U47" s="56" t="s">
         <v>103</v>
       </c>
@@ -11106,7 +11093,7 @@
       <c r="O48" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P48" s="107"/>
+      <c r="P48" s="73"/>
       <c r="Q48" s="56" t="s">
         <v>103</v>
       </c>
@@ -11180,7 +11167,7 @@
       <c r="K50" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L50" s="107"/>
+      <c r="L50" s="73"/>
       <c r="M50" s="56" t="s">
         <v>103</v>
       </c>
@@ -11188,14 +11175,14 @@
       <c r="O50" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="P50" s="107"/>
+      <c r="P50" s="73"/>
       <c r="Q50" s="56" t="s">
         <v>103</v>
       </c>
       <c r="S50" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T50" s="107"/>
+      <c r="T50" s="73"/>
       <c r="U50" s="56" t="s">
         <v>103</v>
       </c>
@@ -11236,7 +11223,7 @@
       <c r="S51" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="T51" s="107"/>
+      <c r="T51" s="73"/>
       <c r="U51" s="56" t="s">
         <v>103</v>
       </c>
@@ -11289,54 +11276,54 @@
       <c r="V52" s="63"/>
     </row>
     <row r="53" spans="1:114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="177" t="s">
+      <c r="A53" s="190" t="s">
         <v>115</v>
       </c>
-      <c r="B53" s="168"/>
-      <c r="C53" s="168"/>
-      <c r="D53" s="168"/>
-      <c r="E53" s="168"/>
-      <c r="F53" s="168"/>
-      <c r="G53" s="168"/>
-      <c r="H53" s="168"/>
-      <c r="I53" s="168"/>
-      <c r="J53" s="168"/>
-      <c r="K53" s="168"/>
-      <c r="L53" s="168"/>
-      <c r="M53" s="168"/>
-      <c r="N53" s="168"/>
-      <c r="O53" s="168"/>
-      <c r="P53" s="168"/>
-      <c r="Q53" s="168"/>
-      <c r="R53" s="168"/>
-      <c r="S53" s="168"/>
-      <c r="T53" s="168"/>
-      <c r="U53" s="168"/>
+      <c r="B53" s="181"/>
+      <c r="C53" s="181"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="181"/>
+      <c r="G53" s="181"/>
+      <c r="H53" s="181"/>
+      <c r="I53" s="181"/>
+      <c r="J53" s="181"/>
+      <c r="K53" s="181"/>
+      <c r="L53" s="181"/>
+      <c r="M53" s="181"/>
+      <c r="N53" s="181"/>
+      <c r="O53" s="181"/>
+      <c r="P53" s="181"/>
+      <c r="Q53" s="181"/>
+      <c r="R53" s="181"/>
+      <c r="S53" s="181"/>
+      <c r="T53" s="181"/>
+      <c r="U53" s="181"/>
     </row>
     <row r="54" spans="1:114" s="22" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="154" t="s">
+      <c r="A54" s="167" t="s">
         <v>184</v>
       </c>
-      <c r="B54" s="154"/>
-      <c r="C54" s="154"/>
-      <c r="D54" s="154"/>
-      <c r="E54" s="154"/>
-      <c r="F54" s="154"/>
-      <c r="G54" s="154"/>
-      <c r="H54" s="154"/>
-      <c r="I54" s="154"/>
-      <c r="J54" s="154"/>
-      <c r="K54" s="154"/>
-      <c r="L54" s="154"/>
-      <c r="M54" s="154"/>
-      <c r="N54" s="154"/>
-      <c r="O54" s="154"/>
-      <c r="P54" s="154"/>
-      <c r="Q54" s="154"/>
-      <c r="R54" s="154"/>
-      <c r="S54" s="154"/>
-      <c r="T54" s="154"/>
-      <c r="U54" s="154"/>
+      <c r="B54" s="167"/>
+      <c r="C54" s="167"/>
+      <c r="D54" s="167"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="167"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
+      <c r="J54" s="167"/>
+      <c r="K54" s="167"/>
+      <c r="L54" s="167"/>
+      <c r="M54" s="167"/>
+      <c r="N54" s="167"/>
+      <c r="O54" s="167"/>
+      <c r="P54" s="167"/>
+      <c r="Q54" s="167"/>
+      <c r="R54" s="167"/>
+      <c r="S54" s="167"/>
+      <c r="T54" s="167"/>
+      <c r="U54" s="167"/>
       <c r="V54" s="26"/>
       <c r="W54" s="26"/>
       <c r="X54" s="26"/>
@@ -11432,29 +11419,29 @@
       <c r="DJ54" s="26"/>
     </row>
     <row r="55" spans="1:114" s="22" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="168" t="s">
+      <c r="A55" s="181" t="s">
         <v>180</v>
       </c>
-      <c r="B55" s="168"/>
-      <c r="C55" s="169"/>
-      <c r="D55" s="169"/>
-      <c r="E55" s="169"/>
-      <c r="F55" s="169"/>
-      <c r="G55" s="169"/>
-      <c r="H55" s="169"/>
-      <c r="I55" s="169"/>
-      <c r="J55" s="169"/>
-      <c r="K55" s="169"/>
-      <c r="L55" s="169"/>
-      <c r="M55" s="169"/>
-      <c r="N55" s="169"/>
-      <c r="O55" s="169"/>
-      <c r="P55" s="169"/>
-      <c r="Q55" s="169"/>
-      <c r="R55" s="169"/>
-      <c r="S55" s="169"/>
-      <c r="T55" s="169"/>
-      <c r="U55" s="169"/>
+      <c r="B55" s="181"/>
+      <c r="C55" s="182"/>
+      <c r="D55" s="182"/>
+      <c r="E55" s="182"/>
+      <c r="F55" s="182"/>
+      <c r="G55" s="182"/>
+      <c r="H55" s="182"/>
+      <c r="I55" s="182"/>
+      <c r="J55" s="182"/>
+      <c r="K55" s="182"/>
+      <c r="L55" s="182"/>
+      <c r="M55" s="182"/>
+      <c r="N55" s="182"/>
+      <c r="O55" s="182"/>
+      <c r="P55" s="182"/>
+      <c r="Q55" s="182"/>
+      <c r="R55" s="182"/>
+      <c r="S55" s="182"/>
+      <c r="T55" s="182"/>
+      <c r="U55" s="182"/>
       <c r="V55" s="26"/>
       <c r="W55" s="26"/>
       <c r="X55" s="26"/>
@@ -11550,77 +11537,77 @@
       <c r="DJ55" s="26"/>
     </row>
     <row r="56" spans="1:114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="156" t="s">
+      <c r="A56" s="169" t="s">
         <v>181</v>
       </c>
-      <c r="B56" s="154"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="154"/>
-      <c r="E56" s="154"/>
-      <c r="F56" s="154"/>
-      <c r="G56" s="154"/>
-      <c r="H56" s="154"/>
-      <c r="I56" s="154"/>
-      <c r="J56" s="154"/>
-      <c r="K56" s="154"/>
-      <c r="L56" s="154"/>
-      <c r="M56" s="154"/>
-      <c r="N56" s="154"/>
-      <c r="O56" s="154"/>
-      <c r="P56" s="154"/>
-      <c r="Q56" s="154"/>
-      <c r="R56" s="155"/>
-      <c r="S56" s="155"/>
-      <c r="T56" s="155"/>
-      <c r="U56" s="155"/>
+      <c r="B56" s="167"/>
+      <c r="C56" s="167"/>
+      <c r="D56" s="167"/>
+      <c r="E56" s="167"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="167"/>
+      <c r="H56" s="167"/>
+      <c r="I56" s="167"/>
+      <c r="J56" s="167"/>
+      <c r="K56" s="167"/>
+      <c r="L56" s="167"/>
+      <c r="M56" s="167"/>
+      <c r="N56" s="167"/>
+      <c r="O56" s="167"/>
+      <c r="P56" s="167"/>
+      <c r="Q56" s="167"/>
+      <c r="R56" s="168"/>
+      <c r="S56" s="168"/>
+      <c r="T56" s="168"/>
+      <c r="U56" s="168"/>
     </row>
     <row r="57" spans="1:114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="154"/>
-      <c r="B57" s="154"/>
-      <c r="C57" s="154"/>
-      <c r="D57" s="154"/>
-      <c r="E57" s="154"/>
-      <c r="F57" s="154"/>
-      <c r="G57" s="154"/>
-      <c r="H57" s="154"/>
-      <c r="I57" s="154"/>
-      <c r="J57" s="154"/>
-      <c r="K57" s="154"/>
-      <c r="L57" s="154"/>
-      <c r="M57" s="154"/>
-      <c r="N57" s="154"/>
-      <c r="O57" s="154"/>
-      <c r="P57" s="154"/>
-      <c r="Q57" s="154"/>
-      <c r="R57" s="176"/>
-      <c r="S57" s="176"/>
-      <c r="T57" s="176"/>
-      <c r="U57" s="176"/>
+      <c r="A57" s="167"/>
+      <c r="B57" s="167"/>
+      <c r="C57" s="167"/>
+      <c r="D57" s="167"/>
+      <c r="E57" s="167"/>
+      <c r="F57" s="167"/>
+      <c r="G57" s="167"/>
+      <c r="H57" s="167"/>
+      <c r="I57" s="167"/>
+      <c r="J57" s="167"/>
+      <c r="K57" s="167"/>
+      <c r="L57" s="167"/>
+      <c r="M57" s="167"/>
+      <c r="N57" s="167"/>
+      <c r="O57" s="167"/>
+      <c r="P57" s="167"/>
+      <c r="Q57" s="167"/>
+      <c r="R57" s="189"/>
+      <c r="S57" s="189"/>
+      <c r="T57" s="189"/>
+      <c r="U57" s="189"/>
     </row>
     <row r="58" spans="1:114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="156" t="s">
+      <c r="A58" s="169" t="s">
         <v>67</v>
       </c>
-      <c r="B58" s="156"/>
-      <c r="C58" s="156"/>
-      <c r="D58" s="156"/>
-      <c r="E58" s="156"/>
-      <c r="F58" s="156"/>
-      <c r="G58" s="156"/>
-      <c r="H58" s="156"/>
-      <c r="I58" s="156"/>
-      <c r="J58" s="156"/>
-      <c r="K58" s="156"/>
-      <c r="L58" s="156"/>
-      <c r="M58" s="156"/>
-      <c r="N58" s="156"/>
-      <c r="O58" s="156"/>
-      <c r="P58" s="156"/>
-      <c r="Q58" s="156"/>
-      <c r="R58" s="176"/>
-      <c r="S58" s="176"/>
-      <c r="T58" s="176"/>
-      <c r="U58" s="176"/>
+      <c r="B58" s="169"/>
+      <c r="C58" s="169"/>
+      <c r="D58" s="169"/>
+      <c r="E58" s="169"/>
+      <c r="F58" s="169"/>
+      <c r="G58" s="169"/>
+      <c r="H58" s="169"/>
+      <c r="I58" s="169"/>
+      <c r="J58" s="169"/>
+      <c r="K58" s="169"/>
+      <c r="L58" s="169"/>
+      <c r="M58" s="169"/>
+      <c r="N58" s="169"/>
+      <c r="O58" s="169"/>
+      <c r="P58" s="169"/>
+      <c r="Q58" s="169"/>
+      <c r="R58" s="189"/>
+      <c r="S58" s="189"/>
+      <c r="T58" s="189"/>
+      <c r="U58" s="189"/>
     </row>
     <row r="59" spans="1:114" x14ac:dyDescent="0.2">
       <c r="C59" s="28"/>
@@ -11695,102 +11682,102 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE970F0C-8730-4E3E-AF19-AD7B112055FB}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.1640625" style="58" customWidth="1"/>
-    <col min="2" max="2" width="2.1640625" style="149" customWidth="1"/>
+    <col min="2" max="2" width="2.1640625" style="73" customWidth="1"/>
     <col min="3" max="3" width="10.1640625" style="67" customWidth="1"/>
-    <col min="4" max="4" width="2.1640625" style="149" customWidth="1"/>
+    <col min="4" max="4" width="2.1640625" style="73" customWidth="1"/>
     <col min="5" max="5" width="10.1640625" style="67" customWidth="1"/>
-    <col min="6" max="6" width="2.1640625" style="149" customWidth="1"/>
+    <col min="6" max="6" width="2.1640625" style="73" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" style="67" customWidth="1"/>
-    <col min="8" max="8" width="3.5" style="149" customWidth="1"/>
+    <col min="8" max="8" width="3.5" style="73" customWidth="1"/>
     <col min="9" max="9" width="10.1640625" style="67" customWidth="1"/>
-    <col min="10" max="10" width="3.5" style="149" customWidth="1"/>
+    <col min="10" max="10" width="3.5" style="73" customWidth="1"/>
     <col min="11" max="11" width="10.1640625" style="67" customWidth="1"/>
-    <col min="12" max="12" width="2.1640625" style="149" customWidth="1"/>
+    <col min="12" max="12" width="2.1640625" style="73" customWidth="1"/>
     <col min="13" max="16384" width="11.5" style="64"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="198" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
       <c r="M1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="198" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="198"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
       <c r="M2" s="51"/>
     </row>
     <row r="3" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="186"/>
-      <c r="B3" s="186"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
-      <c r="L3" s="186"/>
+      <c r="A3" s="199"/>
+      <c r="B3" s="199"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="199"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="199"/>
+      <c r="H3" s="199"/>
+      <c r="I3" s="199"/>
+      <c r="J3" s="199"/>
+      <c r="K3" s="199"/>
+      <c r="L3" s="199"/>
       <c r="M3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="185" t="s">
+      <c r="A4" s="198" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
+      <c r="K4" s="198"/>
+      <c r="L4" s="198"/>
       <c r="M4" s="51"/>
     </row>
     <row r="5" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="187"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="187"/>
-      <c r="D5" s="187"/>
-      <c r="E5" s="187"/>
-      <c r="F5" s="187"/>
-      <c r="G5" s="187"/>
-      <c r="H5" s="187"/>
-      <c r="I5" s="187"/>
-      <c r="J5" s="187"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="187"/>
+      <c r="A5" s="200"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="200"/>
+      <c r="L5" s="200"/>
       <c r="M5" s="51"/>
     </row>
     <row r="6" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11824,7 +11811,7 @@
       <c r="A7" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="150"/>
+      <c r="B7" s="144"/>
       <c r="C7" s="65"/>
       <c r="E7" s="65"/>
       <c r="G7" s="65"/>
@@ -11848,7 +11835,7 @@
       <c r="I8" s="39">
         <v>380</v>
       </c>
-      <c r="J8" s="149" t="s">
+      <c r="J8" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K8" s="39">
@@ -11872,7 +11859,7 @@
       <c r="I9" s="39">
         <v>14591</v>
       </c>
-      <c r="J9" s="149" t="s">
+      <c r="J9" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K9" s="39">
@@ -11890,25 +11877,25 @@
       <c r="E10" s="39">
         <v>2800</v>
       </c>
-      <c r="F10" s="149" t="s">
+      <c r="F10" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G10" s="39">
         <v>2800</v>
       </c>
-      <c r="H10" s="149" t="s">
+      <c r="H10" s="73" t="s">
         <v>168</v>
       </c>
       <c r="I10" s="39">
         <v>2800</v>
       </c>
-      <c r="J10" s="149" t="s">
+      <c r="J10" s="73" t="s">
         <v>168</v>
       </c>
       <c r="K10" s="39">
         <v>2800</v>
       </c>
-      <c r="L10" s="149" t="s">
+      <c r="L10" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M10" s="51"/>
@@ -11950,7 +11937,7 @@
       <c r="I12" s="39">
         <v>90000</v>
       </c>
-      <c r="J12" s="149" t="s">
+      <c r="J12" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K12" s="39">
@@ -11965,31 +11952,31 @@
       <c r="C13" s="39">
         <v>100</v>
       </c>
-      <c r="D13" s="149" t="s">
+      <c r="D13" s="73" t="s">
         <v>128</v>
       </c>
       <c r="E13" s="39">
         <v>100</v>
       </c>
-      <c r="F13" s="149" t="s">
+      <c r="F13" s="73" t="s">
         <v>128</v>
       </c>
       <c r="G13" s="39">
         <v>150</v>
       </c>
-      <c r="H13" s="149" t="s">
+      <c r="H13" s="73" t="s">
         <v>128</v>
       </c>
       <c r="I13" s="39">
         <v>106</v>
       </c>
-      <c r="J13" s="149" t="s">
+      <c r="J13" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K13" s="39">
         <v>100</v>
       </c>
-      <c r="L13" s="149" t="s">
+      <c r="L13" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M13" s="51"/>
@@ -12049,7 +12036,7 @@
       <c r="G16" s="66">
         <v>90</v>
       </c>
-      <c r="H16" s="149" t="s">
+      <c r="H16" s="73" t="s">
         <v>128</v>
       </c>
       <c r="I16" s="66">
@@ -12058,7 +12045,7 @@
       <c r="K16" s="66">
         <v>90</v>
       </c>
-      <c r="L16" s="149" t="s">
+      <c r="L16" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M16" s="51"/>
@@ -12150,7 +12137,7 @@
       <c r="I20" s="39">
         <v>110</v>
       </c>
-      <c r="J20" s="149" t="s">
+      <c r="J20" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K20" s="39">
@@ -12165,25 +12152,25 @@
       <c r="C21" s="39">
         <v>8600</v>
       </c>
-      <c r="D21" s="149" t="s">
+      <c r="D21" s="73" t="s">
         <v>128</v>
       </c>
       <c r="E21" s="39">
         <v>4600</v>
       </c>
-      <c r="F21" s="149" t="s">
+      <c r="F21" s="73" t="s">
         <v>128</v>
       </c>
       <c r="G21" s="39">
         <v>5000</v>
       </c>
-      <c r="H21" s="149" t="s">
+      <c r="H21" s="73" t="s">
         <v>128</v>
       </c>
       <c r="I21" s="39">
         <v>4469</v>
       </c>
-      <c r="J21" s="149" t="s">
+      <c r="J21" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K21" s="39">
@@ -12201,25 +12188,25 @@
       <c r="E22" s="39">
         <v>2800</v>
       </c>
-      <c r="F22" s="149" t="s">
+      <c r="F22" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G22" s="39">
         <v>4200</v>
       </c>
-      <c r="H22" s="149" t="s">
+      <c r="H22" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I22" s="39">
         <v>4100</v>
       </c>
-      <c r="J22" s="149" t="s">
+      <c r="J22" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K22" s="39">
         <v>4000</v>
       </c>
-      <c r="L22" s="149" t="s">
+      <c r="L22" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M22" s="51"/>
@@ -12237,13 +12224,13 @@
       <c r="G23" s="39">
         <v>618</v>
       </c>
-      <c r="H23" s="149" t="s">
+      <c r="H23" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I23" s="39">
         <v>501</v>
       </c>
-      <c r="J23" s="149" t="s">
+      <c r="J23" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K23" s="39">
@@ -12309,7 +12296,7 @@
       <c r="I26" s="39">
         <v>21000</v>
       </c>
-      <c r="J26" s="149" t="s">
+      <c r="J26" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K26" s="39">
@@ -12324,25 +12311,25 @@
       <c r="C27" s="39">
         <v>10</v>
       </c>
-      <c r="D27" s="149" t="s">
+      <c r="D27" s="73" t="s">
         <v>128</v>
       </c>
       <c r="E27" s="39">
         <v>20</v>
       </c>
-      <c r="F27" s="149" t="s">
+      <c r="F27" s="73" t="s">
         <v>128</v>
       </c>
       <c r="G27" s="39">
         <v>20</v>
       </c>
-      <c r="H27" s="149" t="s">
+      <c r="H27" s="73" t="s">
         <v>128</v>
       </c>
       <c r="I27" s="39">
         <v>15</v>
       </c>
-      <c r="J27" s="149" t="s">
+      <c r="J27" s="73" t="s">
         <v>128</v>
       </c>
       <c r="K27" s="39">
@@ -12482,7 +12469,7 @@
       <c r="C34" s="39">
         <v>340</v>
       </c>
-      <c r="D34" s="149" t="s">
+      <c r="D34" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E34" s="39">
@@ -12536,7 +12523,7 @@
       <c r="I36" s="66">
         <v>473</v>
       </c>
-      <c r="J36" s="149" t="s">
+      <c r="J36" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K36" s="39">
@@ -12591,7 +12578,7 @@
       <c r="E39" s="39">
         <v>410</v>
       </c>
-      <c r="F39" s="149" t="s">
+      <c r="F39" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G39" s="39">
@@ -12600,7 +12587,7 @@
       <c r="I39" s="39">
         <v>290</v>
       </c>
-      <c r="J39" s="149" t="s">
+      <c r="J39" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K39" s="39">
@@ -12624,13 +12611,13 @@
       <c r="I40" s="39">
         <v>1500</v>
       </c>
-      <c r="J40" s="149" t="s">
+      <c r="J40" s="73" t="s">
         <v>128</v>
       </c>
       <c r="K40" s="39">
         <v>1600</v>
       </c>
-      <c r="L40" s="149" t="s">
+      <c r="L40" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M40" s="51"/>
@@ -12792,7 +12779,7 @@
       <c r="G48" s="39">
         <v>1249</v>
       </c>
-      <c r="H48" s="149" t="s">
+      <c r="H48" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I48" s="39">
@@ -12839,19 +12826,19 @@
       <c r="E50" s="39">
         <v>420000</v>
       </c>
-      <c r="F50" s="149" t="s">
+      <c r="F50" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G50" s="39">
         <v>475000</v>
       </c>
-      <c r="H50" s="149" t="s">
+      <c r="H50" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I50" s="39">
         <v>441000</v>
       </c>
-      <c r="J50" s="149" t="s">
+      <c r="J50" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K50" s="39">
@@ -12860,92 +12847,92 @@
       <c r="M50" s="51"/>
     </row>
     <row r="51" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="188" t="s">
+      <c r="A51" s="201" t="s">
         <v>155</v>
       </c>
-      <c r="B51" s="188"/>
-      <c r="C51" s="188"/>
-      <c r="D51" s="188"/>
-      <c r="E51" s="188"/>
-      <c r="F51" s="188"/>
-      <c r="G51" s="188"/>
-      <c r="H51" s="188"/>
-      <c r="I51" s="188"/>
-      <c r="J51" s="188"/>
-      <c r="K51" s="188"/>
-      <c r="L51" s="188"/>
+      <c r="B51" s="201"/>
+      <c r="C51" s="201"/>
+      <c r="D51" s="201"/>
+      <c r="E51" s="201"/>
+      <c r="F51" s="201"/>
+      <c r="G51" s="201"/>
+      <c r="H51" s="201"/>
+      <c r="I51" s="201"/>
+      <c r="J51" s="201"/>
+      <c r="K51" s="201"/>
+      <c r="L51" s="201"/>
       <c r="M51" s="57"/>
       <c r="N51" s="57"/>
     </row>
-    <row r="52" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="183" t="s">
+    <row r="52" spans="1:14" ht="33.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="196" t="s">
         <v>170</v>
       </c>
-      <c r="B52" s="183"/>
-      <c r="C52" s="183"/>
-      <c r="D52" s="183"/>
-      <c r="E52" s="183"/>
-      <c r="F52" s="183"/>
-      <c r="G52" s="183"/>
-      <c r="H52" s="183"/>
-      <c r="I52" s="183"/>
-      <c r="J52" s="183"/>
-      <c r="K52" s="183"/>
-      <c r="L52" s="183"/>
+      <c r="B52" s="196"/>
+      <c r="C52" s="196"/>
+      <c r="D52" s="196"/>
+      <c r="E52" s="196"/>
+      <c r="F52" s="196"/>
+      <c r="G52" s="196"/>
+      <c r="H52" s="196"/>
+      <c r="I52" s="196"/>
+      <c r="J52" s="196"/>
+      <c r="K52" s="196"/>
+      <c r="L52" s="196"/>
       <c r="M52" s="57"/>
       <c r="N52" s="57"/>
     </row>
-    <row r="53" spans="1:14" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="184" t="s">
+    <row r="53" spans="1:14" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="197" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="184"/>
-      <c r="C53" s="184"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="184"/>
-      <c r="F53" s="184"/>
-      <c r="G53" s="184"/>
-      <c r="H53" s="184"/>
-      <c r="I53" s="184"/>
-      <c r="J53" s="184"/>
-      <c r="K53" s="184"/>
-      <c r="L53" s="184"/>
+      <c r="B53" s="197"/>
+      <c r="C53" s="197"/>
+      <c r="D53" s="197"/>
+      <c r="E53" s="197"/>
+      <c r="F53" s="197"/>
+      <c r="G53" s="197"/>
+      <c r="H53" s="197"/>
+      <c r="I53" s="197"/>
+      <c r="J53" s="197"/>
+      <c r="K53" s="197"/>
+      <c r="L53" s="197"/>
       <c r="M53" s="57"/>
       <c r="N53" s="57"/>
     </row>
     <row r="54" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="183" t="s">
+      <c r="A54" s="196" t="s">
         <v>185</v>
       </c>
-      <c r="B54" s="183"/>
-      <c r="C54" s="183"/>
-      <c r="D54" s="183"/>
-      <c r="E54" s="183"/>
-      <c r="F54" s="183"/>
-      <c r="G54" s="183"/>
-      <c r="H54" s="183"/>
-      <c r="I54" s="183"/>
-      <c r="J54" s="183"/>
-      <c r="K54" s="183"/>
-      <c r="L54" s="183"/>
+      <c r="B54" s="196"/>
+      <c r="C54" s="196"/>
+      <c r="D54" s="196"/>
+      <c r="E54" s="196"/>
+      <c r="F54" s="196"/>
+      <c r="G54" s="196"/>
+      <c r="H54" s="196"/>
+      <c r="I54" s="196"/>
+      <c r="J54" s="196"/>
+      <c r="K54" s="196"/>
+      <c r="L54" s="196"/>
       <c r="M54" s="57"/>
       <c r="N54" s="57"/>
     </row>
     <row r="55" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="184" t="s">
+      <c r="A55" s="197" t="s">
         <v>157</v>
       </c>
-      <c r="B55" s="184"/>
-      <c r="C55" s="184"/>
-      <c r="D55" s="184"/>
-      <c r="E55" s="184"/>
-      <c r="F55" s="184"/>
-      <c r="G55" s="184"/>
-      <c r="H55" s="184"/>
-      <c r="I55" s="184"/>
-      <c r="J55" s="184"/>
-      <c r="K55" s="184"/>
-      <c r="L55" s="184"/>
+      <c r="B55" s="197"/>
+      <c r="C55" s="197"/>
+      <c r="D55" s="197"/>
+      <c r="E55" s="197"/>
+      <c r="F55" s="197"/>
+      <c r="G55" s="197"/>
+      <c r="H55" s="197"/>
+      <c r="I55" s="197"/>
+      <c r="J55" s="197"/>
+      <c r="K55" s="197"/>
+      <c r="L55" s="197"/>
       <c r="M55" s="57"/>
       <c r="N55" s="57"/>
     </row>
@@ -12970,102 +12957,102 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591A6079-14DC-4E03-A6AE-42FE94D68C4A}">
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="58" customWidth="1"/>
-    <col min="2" max="2" width="2.1640625" style="149" customWidth="1"/>
+    <col min="2" max="2" width="2.1640625" style="73" customWidth="1"/>
     <col min="3" max="3" width="10.1640625" style="67" customWidth="1"/>
-    <col min="4" max="4" width="2.1640625" style="149" customWidth="1"/>
+    <col min="4" max="4" width="2.1640625" style="73" customWidth="1"/>
     <col min="5" max="5" width="10.1640625" style="67" customWidth="1"/>
-    <col min="6" max="6" width="2.1640625" style="149" customWidth="1"/>
+    <col min="6" max="6" width="2.1640625" style="73" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" style="67" customWidth="1"/>
-    <col min="8" max="8" width="2.1640625" style="149" customWidth="1"/>
+    <col min="8" max="8" width="2.1640625" style="73" customWidth="1"/>
     <col min="9" max="9" width="10.1640625" style="67" customWidth="1"/>
-    <col min="10" max="10" width="3.5" style="149" customWidth="1"/>
+    <col min="10" max="10" width="3.5" style="73" customWidth="1"/>
     <col min="11" max="11" width="10.1640625" style="67" customWidth="1"/>
-    <col min="12" max="12" width="2.1640625" style="149" customWidth="1"/>
+    <col min="12" max="12" width="2.1640625" style="73" customWidth="1"/>
     <col min="13" max="16384" width="11.5" style="64"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="198" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
       <c r="M1" s="51"/>
     </row>
     <row r="2" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="198" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="198"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
       <c r="M2" s="51"/>
     </row>
     <row r="3" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="186"/>
-      <c r="B3" s="186"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186"/>
-      <c r="J3" s="186"/>
-      <c r="K3" s="186"/>
-      <c r="L3" s="186"/>
+      <c r="A3" s="199"/>
+      <c r="B3" s="199"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="199"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="199"/>
+      <c r="H3" s="199"/>
+      <c r="I3" s="199"/>
+      <c r="J3" s="199"/>
+      <c r="K3" s="199"/>
+      <c r="L3" s="199"/>
       <c r="M3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="185" t="s">
+      <c r="A4" s="198" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
+      <c r="K4" s="198"/>
+      <c r="L4" s="198"/>
       <c r="M4" s="51"/>
     </row>
     <row r="5" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="187"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="187"/>
-      <c r="D5" s="187"/>
-      <c r="E5" s="187"/>
-      <c r="F5" s="187"/>
-      <c r="G5" s="187"/>
-      <c r="H5" s="187"/>
-      <c r="I5" s="187"/>
-      <c r="J5" s="187"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="187"/>
+      <c r="A5" s="200"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="200"/>
+      <c r="L5" s="200"/>
       <c r="M5" s="51"/>
     </row>
     <row r="6" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13123,7 +13110,7 @@
       <c r="I8" s="39">
         <v>35000</v>
       </c>
-      <c r="J8" s="149" t="s">
+      <c r="J8" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K8" s="39">
@@ -13138,31 +13125,31 @@
       <c r="C9" s="39">
         <v>2379</v>
       </c>
-      <c r="D9" s="149" t="s">
+      <c r="D9" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E9" s="39">
         <v>1387</v>
       </c>
-      <c r="F9" s="149" t="s">
+      <c r="F9" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G9" s="39">
         <v>1969</v>
       </c>
-      <c r="H9" s="149" t="s">
+      <c r="H9" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I9" s="39">
         <v>1900</v>
       </c>
-      <c r="J9" s="149" t="s">
+      <c r="J9" s="73" t="s">
         <v>168</v>
       </c>
       <c r="K9" s="39">
         <v>1700</v>
       </c>
-      <c r="L9" s="149" t="s">
+      <c r="L9" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M9" s="51"/>
@@ -13220,13 +13207,13 @@
       <c r="I12" s="39">
         <v>4500</v>
       </c>
-      <c r="J12" s="149" t="s">
+      <c r="J12" s="73" t="s">
         <v>128</v>
       </c>
       <c r="K12" s="39">
         <v>4500</v>
       </c>
-      <c r="L12" s="149" t="s">
+      <c r="L12" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M12" s="51"/>
@@ -13270,27 +13257,24 @@
       <c r="C14" s="66">
         <v>27400</v>
       </c>
-      <c r="D14" s="152"/>
       <c r="E14" s="66">
         <v>28300</v>
       </c>
-      <c r="F14" s="152"/>
       <c r="G14" s="66">
         <v>27500</v>
       </c>
-      <c r="H14" s="152" t="s">
+      <c r="H14" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I14" s="66">
         <v>30500</v>
       </c>
-      <c r="J14" s="152" t="s">
+      <c r="J14" s="73" t="s">
         <v>171</v>
       </c>
       <c r="K14" s="66">
         <v>24500</v>
       </c>
-      <c r="L14" s="152"/>
       <c r="M14" s="51"/>
     </row>
     <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13321,25 +13305,25 @@
       <c r="C16" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="149" t="s">
+      <c r="D16" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E16" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="149" t="s">
+      <c r="F16" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G16" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="149" t="s">
+      <c r="H16" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I16" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="149" t="s">
+      <c r="J16" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K16" s="67" t="s">
@@ -13357,7 +13341,7 @@
       <c r="E17" s="39">
         <v>87410</v>
       </c>
-      <c r="F17" s="149" t="s">
+      <c r="F17" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G17" s="39">
@@ -13378,25 +13362,25 @@
       <c r="C18" s="39">
         <v>81900</v>
       </c>
-      <c r="D18" s="149" t="s">
+      <c r="D18" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E18" s="39">
         <v>69400</v>
       </c>
-      <c r="F18" s="149" t="s">
+      <c r="F18" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G18" s="39">
         <v>98300</v>
       </c>
-      <c r="H18" s="149" t="s">
+      <c r="H18" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I18" s="39">
         <v>82800</v>
       </c>
-      <c r="J18" s="149" t="s">
+      <c r="J18" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K18" s="39">
@@ -13432,25 +13416,25 @@
       <c r="C20" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="149" t="s">
+      <c r="D20" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E20" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="149" t="s">
+      <c r="F20" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G20" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="149" t="s">
+      <c r="H20" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I20" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J20" s="149" t="s">
+      <c r="J20" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K20" s="67" t="s">
@@ -13465,25 +13449,25 @@
       <c r="C21" s="39">
         <v>65800</v>
       </c>
-      <c r="D21" s="149" t="s">
+      <c r="D21" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E21" s="39">
         <v>53300</v>
       </c>
-      <c r="F21" s="149" t="s">
+      <c r="F21" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G21" s="39">
         <v>78700</v>
       </c>
-      <c r="H21" s="149" t="s">
+      <c r="H21" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I21" s="39">
         <v>56100</v>
       </c>
-      <c r="J21" s="149" t="s">
+      <c r="J21" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K21" s="39">
@@ -13498,31 +13482,31 @@
       <c r="C22" s="44">
         <v>377000</v>
       </c>
-      <c r="D22" s="151" t="s">
+      <c r="D22" s="145" t="s">
         <v>160</v>
       </c>
       <c r="E22" s="44">
         <v>320000</v>
       </c>
-      <c r="F22" s="151" t="s">
+      <c r="F22" s="145" t="s">
         <v>160</v>
       </c>
       <c r="G22" s="44">
         <v>360000</v>
       </c>
-      <c r="H22" s="151" t="s">
+      <c r="H22" s="145" t="s">
         <v>160</v>
       </c>
       <c r="I22" s="44">
         <v>344000</v>
       </c>
-      <c r="J22" s="151" t="s">
+      <c r="J22" s="145" t="s">
         <v>160</v>
       </c>
-      <c r="K22" s="44">
+      <c r="K22" s="202">
         <v>322000</v>
       </c>
-      <c r="L22" s="151"/>
+      <c r="L22" s="145"/>
       <c r="M22" s="51"/>
     </row>
     <row r="23" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13564,31 +13548,31 @@
       <c r="C25" s="39">
         <v>1326</v>
       </c>
-      <c r="D25" s="149" t="s">
+      <c r="D25" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E25" s="39">
         <v>1401</v>
       </c>
-      <c r="F25" s="149" t="s">
+      <c r="F25" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G25" s="39">
         <v>1665</v>
       </c>
-      <c r="H25" s="149" t="s">
+      <c r="H25" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I25" s="39">
         <v>1400</v>
       </c>
-      <c r="J25" s="149" t="s">
+      <c r="J25" s="73" t="s">
         <v>168</v>
       </c>
       <c r="K25" s="39">
         <v>1100</v>
       </c>
-      <c r="L25" s="149" t="s">
+      <c r="L25" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M25" s="51"/>
@@ -13650,13 +13634,13 @@
       <c r="I28" s="39">
         <v>1200</v>
       </c>
-      <c r="J28" s="149" t="s">
+      <c r="J28" s="73" t="s">
         <v>128</v>
       </c>
       <c r="K28" s="39">
         <v>1200</v>
       </c>
-      <c r="L28" s="149" t="s">
+      <c r="L28" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M28" s="51"/>
@@ -13674,19 +13658,19 @@
       <c r="G29" s="39">
         <v>12000</v>
       </c>
-      <c r="H29" s="149" t="s">
+      <c r="H29" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I29" s="39">
         <v>12000</v>
       </c>
-      <c r="J29" s="149" t="s">
+      <c r="J29" s="73" t="s">
         <v>168</v>
       </c>
       <c r="K29" s="39">
         <v>12000</v>
       </c>
-      <c r="L29" s="149" t="s">
+      <c r="L29" s="73" t="s">
         <v>128</v>
       </c>
       <c r="M29" s="51"/>
@@ -13698,27 +13682,27 @@
       <c r="C30" s="44">
         <v>14300</v>
       </c>
-      <c r="D30" s="151"/>
+      <c r="D30" s="145"/>
       <c r="E30" s="44">
         <v>12300</v>
       </c>
-      <c r="F30" s="151"/>
+      <c r="F30" s="145"/>
       <c r="G30" s="44">
         <v>13200</v>
       </c>
-      <c r="H30" s="151" t="s">
+      <c r="H30" s="145" t="s">
         <v>160</v>
       </c>
       <c r="I30" s="44">
         <v>13200</v>
       </c>
-      <c r="J30" s="151" t="s">
+      <c r="J30" s="145" t="s">
         <v>171</v>
       </c>
       <c r="K30" s="44">
         <v>13200</v>
       </c>
-      <c r="L30" s="151"/>
+      <c r="L30" s="145"/>
       <c r="M30" s="51"/>
     </row>
     <row r="31" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13749,25 +13733,25 @@
       <c r="C32" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="149" t="s">
+      <c r="D32" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E32" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="F32" s="149" t="s">
+      <c r="F32" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G32" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="149" t="s">
+      <c r="H32" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I32" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J32" s="149" t="s">
+      <c r="J32" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K32" s="67" t="s">
@@ -13803,25 +13787,25 @@
       <c r="C34" s="39">
         <v>132500</v>
       </c>
-      <c r="D34" s="149" t="s">
+      <c r="D34" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E34" s="39">
         <v>105870</v>
       </c>
-      <c r="F34" s="149" t="s">
+      <c r="F34" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G34" s="39">
         <v>149870</v>
       </c>
-      <c r="H34" s="149" t="s">
+      <c r="H34" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I34" s="39">
         <v>126000</v>
       </c>
-      <c r="J34" s="149" t="s">
+      <c r="J34" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K34" s="39">
@@ -13857,25 +13841,25 @@
       <c r="C36" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="149" t="s">
+      <c r="D36" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E36" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="149" t="s">
+      <c r="F36" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G36" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="H36" s="149" t="s">
+      <c r="H36" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I36" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J36" s="149" t="s">
+      <c r="J36" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K36" s="67" t="s">
@@ -13890,25 +13874,25 @@
       <c r="C37" s="39">
         <v>37900</v>
       </c>
-      <c r="D37" s="149" t="s">
+      <c r="D37" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E37" s="39">
         <v>38300</v>
       </c>
-      <c r="F37" s="149" t="s">
+      <c r="F37" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G37" s="39">
         <v>40800</v>
       </c>
-      <c r="H37" s="149" t="s">
+      <c r="H37" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I37" s="39">
         <v>32100</v>
       </c>
-      <c r="J37" s="149" t="s">
+      <c r="J37" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K37" s="39">
@@ -13944,11 +13928,11 @@
       <c r="J38" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="K38" s="49">
+      <c r="K38" s="203">
         <v>274000</v>
       </c>
       <c r="L38" s="50"/>
-      <c r="M38" s="153"/>
+      <c r="M38" s="146"/>
     </row>
     <row r="39" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="68" t="s">
@@ -13957,25 +13941,25 @@
       <c r="C39" s="39">
         <v>670000</v>
       </c>
-      <c r="D39" s="149" t="s">
+      <c r="D39" s="73" t="s">
         <v>160</v>
       </c>
       <c r="E39" s="39">
         <v>608000</v>
       </c>
-      <c r="F39" s="149" t="s">
+      <c r="F39" s="73" t="s">
         <v>160</v>
       </c>
       <c r="G39" s="39">
         <v>673000</v>
       </c>
-      <c r="H39" s="149" t="s">
+      <c r="H39" s="73" t="s">
         <v>160</v>
       </c>
       <c r="I39" s="39">
         <v>612000</v>
       </c>
-      <c r="J39" s="149" t="s">
+      <c r="J39" s="73" t="s">
         <v>160</v>
       </c>
       <c r="K39" s="39">
@@ -13984,110 +13968,110 @@
       <c r="M39" s="51"/>
     </row>
     <row r="40" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="188" t="s">
+      <c r="A40" s="201" t="s">
         <v>155</v>
       </c>
-      <c r="B40" s="188"/>
-      <c r="C40" s="188"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="188"/>
-      <c r="G40" s="188"/>
-      <c r="H40" s="188"/>
-      <c r="I40" s="188"/>
-      <c r="J40" s="188"/>
-      <c r="K40" s="188"/>
-      <c r="L40" s="188"/>
+      <c r="B40" s="201"/>
+      <c r="C40" s="201"/>
+      <c r="D40" s="201"/>
+      <c r="E40" s="201"/>
+      <c r="F40" s="201"/>
+      <c r="G40" s="201"/>
+      <c r="H40" s="201"/>
+      <c r="I40" s="201"/>
+      <c r="J40" s="201"/>
+      <c r="K40" s="201"/>
+      <c r="L40" s="201"/>
       <c r="M40" s="57"/>
       <c r="N40" s="57"/>
     </row>
-    <row r="41" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="183" t="s">
+    <row r="41" spans="1:14" ht="33.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="196" t="s">
         <v>173</v>
       </c>
-      <c r="B41" s="183"/>
-      <c r="C41" s="183"/>
-      <c r="D41" s="183"/>
-      <c r="E41" s="183"/>
-      <c r="F41" s="183"/>
-      <c r="G41" s="183"/>
-      <c r="H41" s="183"/>
-      <c r="I41" s="183"/>
-      <c r="J41" s="183"/>
-      <c r="K41" s="183"/>
-      <c r="L41" s="183"/>
+      <c r="B41" s="196"/>
+      <c r="C41" s="196"/>
+      <c r="D41" s="196"/>
+      <c r="E41" s="196"/>
+      <c r="F41" s="196"/>
+      <c r="G41" s="196"/>
+      <c r="H41" s="196"/>
+      <c r="I41" s="196"/>
+      <c r="J41" s="196"/>
+      <c r="K41" s="196"/>
+      <c r="L41" s="196"/>
       <c r="M41" s="57"/>
       <c r="N41" s="57"/>
     </row>
     <row r="42" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="184" t="s">
+      <c r="A42" s="197" t="s">
         <v>137</v>
       </c>
-      <c r="B42" s="184"/>
-      <c r="C42" s="184"/>
-      <c r="D42" s="184"/>
-      <c r="E42" s="184"/>
-      <c r="F42" s="184"/>
-      <c r="G42" s="184"/>
-      <c r="H42" s="184"/>
-      <c r="I42" s="184"/>
-      <c r="J42" s="184"/>
-      <c r="K42" s="184"/>
-      <c r="L42" s="184"/>
+      <c r="B42" s="197"/>
+      <c r="C42" s="197"/>
+      <c r="D42" s="197"/>
+      <c r="E42" s="197"/>
+      <c r="F42" s="197"/>
+      <c r="G42" s="197"/>
+      <c r="H42" s="197"/>
+      <c r="I42" s="197"/>
+      <c r="J42" s="197"/>
+      <c r="K42" s="197"/>
+      <c r="L42" s="197"/>
       <c r="M42" s="57"/>
       <c r="N42" s="57"/>
     </row>
     <row r="43" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="184" t="s">
+      <c r="A43" s="197" t="s">
         <v>138</v>
       </c>
-      <c r="B43" s="184"/>
-      <c r="C43" s="184"/>
-      <c r="D43" s="184"/>
-      <c r="E43" s="184"/>
-      <c r="F43" s="184"/>
-      <c r="G43" s="184"/>
-      <c r="H43" s="184"/>
-      <c r="I43" s="184"/>
-      <c r="J43" s="184"/>
-      <c r="K43" s="184"/>
-      <c r="L43" s="184"/>
+      <c r="B43" s="197"/>
+      <c r="C43" s="197"/>
+      <c r="D43" s="197"/>
+      <c r="E43" s="197"/>
+      <c r="F43" s="197"/>
+      <c r="G43" s="197"/>
+      <c r="H43" s="197"/>
+      <c r="I43" s="197"/>
+      <c r="J43" s="197"/>
+      <c r="K43" s="197"/>
+      <c r="L43" s="197"/>
       <c r="M43" s="57"/>
       <c r="N43" s="57"/>
     </row>
     <row r="44" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="184" t="s">
+      <c r="A44" s="197" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="184"/>
-      <c r="C44" s="184"/>
-      <c r="D44" s="184"/>
-      <c r="E44" s="184"/>
-      <c r="F44" s="184"/>
-      <c r="G44" s="184"/>
-      <c r="H44" s="184"/>
-      <c r="I44" s="184"/>
-      <c r="J44" s="184"/>
-      <c r="K44" s="184"/>
-      <c r="L44" s="184"/>
+      <c r="B44" s="197"/>
+      <c r="C44" s="197"/>
+      <c r="D44" s="197"/>
+      <c r="E44" s="197"/>
+      <c r="F44" s="197"/>
+      <c r="G44" s="197"/>
+      <c r="H44" s="197"/>
+      <c r="I44" s="197"/>
+      <c r="J44" s="197"/>
+      <c r="K44" s="197"/>
+      <c r="L44" s="197"/>
       <c r="M44" s="57"/>
       <c r="N44" s="57"/>
     </row>
     <row r="45" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="184" t="s">
+      <c r="A45" s="197" t="s">
         <v>140</v>
       </c>
-      <c r="B45" s="184"/>
-      <c r="C45" s="184"/>
-      <c r="D45" s="184"/>
-      <c r="E45" s="184"/>
-      <c r="F45" s="184"/>
-      <c r="G45" s="184"/>
-      <c r="H45" s="184"/>
-      <c r="I45" s="184"/>
-      <c r="J45" s="184"/>
-      <c r="K45" s="184"/>
-      <c r="L45" s="184"/>
+      <c r="B45" s="197"/>
+      <c r="C45" s="197"/>
+      <c r="D45" s="197"/>
+      <c r="E45" s="197"/>
+      <c r="F45" s="197"/>
+      <c r="G45" s="197"/>
+      <c r="H45" s="197"/>
+      <c r="I45" s="197"/>
+      <c r="J45" s="197"/>
+      <c r="K45" s="197"/>
+      <c r="L45" s="197"/>
       <c r="M45" s="57"/>
       <c r="N45" s="57"/>
     </row>
